--- a/workspaces/btc_daily_14days/volume/volume_ratio_30.xlsx
+++ b/workspaces/btc_daily_14days/volume/volume_ratio_30.xlsx
@@ -572,49 +572,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-6.710305790089492</v>
+        <v>-6.860447769541366</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>1.316960637255377</v>
+        <v>1.341933137180085</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>10.01628984661193</v>
+        <v>10.23234882425942</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>6.531202696894589</v>
+        <v>6.671121319756963</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>10.82270687250477</v>
+        <v>11.05776351825644</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>6.295625930130598</v>
+        <v>6.431318755719218</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>5.007856231252575</v>
+        <v>5.113722467061358</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>3.339807837697442</v>
+        <v>3.409983895612832</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>3.279499269565022</v>
+        <v>3.349930674361104</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>6.060439783415639</v>
+        <v>6.19171099961985</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>2.9130128781701</v>
+        <v>2.978551042169414</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>1.741449011147338</v>
+        <v>1.779773275109129</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>1.330984352833852</v>
+        <v>1.360076412764144</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>1.57765247559233</v>
+        <v>1.610138940600095</v>
       </c>
     </row>
     <row r="7">
@@ -624,49 +624,49 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>4.771518944746894</v>
+        <v>4.798451390321624</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>4.015642645999804</v>
+        <v>4.0389048215931</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>1.91088611584032</v>
+        <v>1.922800040147926</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-3.478472072151888</v>
+        <v>-3.499414948883754</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-8.290371481237109</v>
+        <v>-8.339383831156169</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-2.864307967848397</v>
+        <v>-2.8813229035745</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>1.329568259306591</v>
+        <v>1.33717130484581</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.8660899210918771</v>
+        <v>0.8709162439815259</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-2.618882764019368</v>
+        <v>-2.634600526521957</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.8168947442971728</v>
+        <v>0.8222133732009453</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>4.03797414451391</v>
+        <v>4.063160709489587</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.64798522817064</v>
+        <v>0.652170898914747</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-3.19609555627499</v>
+        <v>-3.215173614085153</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-2.948159867136965</v>
+        <v>-2.966276555355641</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>158</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-1.227615535399856</v>
+        <v>-1.223878477693411</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>4.123935401564957</v>
+        <v>4.112943066830617</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>1.829759548560489</v>
+        <v>1.824496905755318</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.6938217879035591</v>
+        <v>0.6922402296392747</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.1552736871400313</v>
+        <v>0.1551173364659348</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>4.886966931556039</v>
+        <v>4.87395749822317</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>1.001908749811918</v>
+        <v>0.9992919499159925</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>1.801869302907221</v>
+        <v>1.797133528857231</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>3.009063291268369</v>
+        <v>3.001164996670745</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>1.524331633966405</v>
+        <v>1.51998320983877</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>2.587738807269901</v>
+        <v>2.580050793412511</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>2.622527098232403</v>
+        <v>2.615293669085233</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>2.83609236258696</v>
+        <v>2.828653222351193</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>2.452390521950001</v>
+        <v>2.446207076246289</v>
       </c>
     </row>
     <row r="9">
@@ -728,49 +728,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>2.095933660466351</v>
+        <v>2.109909747649859</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-1.448379857123619</v>
+        <v>-1.458144216329131</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.5728062708450281</v>
+        <v>0.5786515158426582</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.2634452184844491</v>
+        <v>-0.2660098403157107</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.05300529366296303</v>
+        <v>-0.05410623586028862</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.2413183433061263</v>
+        <v>-0.241938936005937</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>1.608858209545417</v>
+        <v>1.620950949052556</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-1.274428961579964</v>
+        <v>-1.283673424337927</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>1.083261999297022</v>
+        <v>1.091741354703146</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>3.408840693548079</v>
+        <v>3.435467016706994</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>2.720084824313922</v>
+        <v>2.743302947018719</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>3.240681945261414</v>
+        <v>3.266208048944868</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>1.85754869189536</v>
+        <v>1.871763664687684</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.7984366621894594</v>
+        <v>-0.8047963198635131</v>
       </c>
     </row>
     <row r="10">
@@ -780,49 +780,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.4946094885550494</v>
+        <v>0.4953171178992051</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>3.266526307208927</v>
+        <v>3.272668586028615</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.4804251938715396</v>
+        <v>0.4817866311237395</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.1864486215992684</v>
+        <v>-0.1869786627754664</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.07202135773891882</v>
+        <v>0.07196355791086972</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.3697935471493423</v>
+        <v>0.3707587048359855</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>1.88019359181331</v>
+        <v>1.883863613220527</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>1.632571371066703</v>
+        <v>1.635513426140825</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>2.369580434515804</v>
+        <v>2.374176602357196</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.7233171626411803</v>
+        <v>0.7253392918220243</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.9174593550901093</v>
+        <v>0.9202176433792815</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.9526904139086412</v>
+        <v>0.9551578395386997</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>2.130791088504523</v>
+        <v>2.135020825691754</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>3.978298891434996</v>
+        <v>3.985447582575304</v>
       </c>
     </row>
     <row r="11">
@@ -832,49 +832,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-5.95255781706539</v>
+        <v>-5.980435915790338</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-1.904292951588175</v>
+        <v>-1.911622402382164</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-1.041008072263068</v>
+        <v>-1.044366623958375</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.2817146159575117</v>
+        <v>-0.2835837462402679</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>2.325409640509456</v>
+        <v>2.335664454006505</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>2.309332454656257</v>
+        <v>2.320895199925658</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>1.281074146508679</v>
+        <v>1.288200670306239</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.8132334514621959</v>
+        <v>0.8173799548514538</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.1229798957369539</v>
+        <v>0.1249919745385597</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-2.302572036197112</v>
+        <v>-2.311099928108796</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-1.247710588815089</v>
+        <v>-1.250277261907044</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-1.667771521668151</v>
+        <v>-1.673225813244699</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-1.45760132452255</v>
+        <v>-1.46277622225395</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-1.975937146242366</v>
+        <v>-1.98417267058916</v>
       </c>
     </row>
     <row r="12">
@@ -884,49 +884,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1.44595561918397</v>
+        <v>1.449477392307642</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-2.729379976502422</v>
+        <v>-2.742147052065626</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-3.729382590985296</v>
+        <v>-3.746652370056907</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-2.083154211515705</v>
+        <v>-2.094274316517875</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-1.711763752250221</v>
+        <v>-1.719562432690992</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-2.932318296872367</v>
+        <v>-2.944520086234093</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-4.837298112013968</v>
+        <v>-4.859092399142803</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-3.483288833972573</v>
+        <v>-3.499610593952163</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-2.028882180011756</v>
+        <v>-2.03713337693349</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-4.697483199601223</v>
+        <v>-4.719430455108807</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-4.295800107448017</v>
+        <v>-4.313909181782542</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-3.957589707937451</v>
+        <v>-3.975373875772682</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-2.992018077330329</v>
+        <v>-3.005737164335031</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.9221932188386504</v>
+        <v>-0.9267475393758176</v>
       </c>
     </row>
     <row r="13">
@@ -936,49 +936,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-3.370631302666055</v>
+        <v>-3.378859053961065</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-2.350625968261888</v>
+        <v>-2.355812161604547</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-5.084675961408315</v>
+        <v>-5.095519278293708</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-4.662025167981902</v>
+        <v>-4.672504396669801</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.062711511682636</v>
+        <v>0.06270646763957188</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.5193887618151081</v>
+        <v>0.5207651657421692</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.7283851764101499</v>
+        <v>0.7296146530303176</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.3224240227696171</v>
+        <v>-0.3235678767647485</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-3.310884223886326</v>
+        <v>-3.317365428984722</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.06117188061764978</v>
+        <v>-0.0619187665051868</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.437094714770296</v>
+        <v>-1.439692618682002</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-1.987552068469014</v>
+        <v>-1.991819725266325</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>1.397652056851392</v>
+        <v>1.400242379331438</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-1.865038359932591</v>
+        <v>-1.869097871970062</v>
       </c>
     </row>
     <row r="14">
@@ -988,49 +988,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>1.569061679789947</v>
+        <v>1.571082452223266</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-3.16751193317431</v>
+        <v>-3.190958429763903</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-1.062380639770815</v>
+        <v>-1.075363410609761</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-1.244627507163322</v>
+        <v>-1.260129323090311</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-1.158048722235414</v>
+        <v>-1.165744266570556</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-2.110606784519909</v>
+        <v>-2.122288510093462</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-3.899298009498061</v>
+        <v>-3.924062506616451</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-4.989142130428377</v>
+        <v>-5.022530713298508</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-5.501332156799982</v>
+        <v>-5.537989195560947</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-6.970950733898377</v>
+        <v>-7.017045198199007</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-5.614030049405429</v>
+        <v>-5.649471478491421</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-5.264944248888142</v>
+        <v>-5.300622912340891</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-5.685474190229534</v>
+        <v>-5.720877523285864</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-2.934376205970871</v>
+        <v>-2.955432920569258</v>
       </c>
     </row>
     <row r="15">
@@ -2213,10 +2213,8 @@
           <t>X &gt; 0.4514</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>4065~4078</t>
-        </is>
+      <c r="B6" t="n">
+        <v>4065</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>0.1549187175536275</v>
@@ -2267,10 +2265,8 @@
           <t>X &gt; 0.5113</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>3984~3995</t>
-        </is>
+      <c r="B7" t="n">
+        <v>3984</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>0.2975504157099209</v>
@@ -2321,10 +2317,8 @@
           <t>X &gt; 0.5712</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>3868~3878</t>
-        </is>
+      <c r="B8" t="n">
+        <v>3868</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>0.1625699314661446</v>
@@ -2375,10 +2369,8 @@
           <t>X &gt; 0.631</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>3710~3720</t>
-        </is>
+      <c r="B9" t="n">
+        <v>3710</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>0.2216154432308812</v>
@@ -2429,10 +2421,8 @@
           <t>X &gt; 0.6909</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>3505~3513</t>
-        </is>
+      <c r="B10" t="n">
+        <v>3505</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>0.1111731230009596</v>
@@ -2483,10 +2473,8 @@
           <t>X &gt; 0.7507</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>3255~3262</t>
-        </is>
+      <c r="B11" t="n">
+        <v>3255</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>0.08166897592735722</v>
@@ -2537,10 +2525,8 @@
           <t>X &gt; 0.8106</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2939~2944</t>
-        </is>
+      <c r="B12" t="n">
+        <v>2939</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>0.7334638537030713</v>
@@ -2591,10 +2577,8 @@
           <t>X &gt; 0.8704</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2611~2614</t>
-        </is>
+      <c r="B13" t="n">
+        <v>2611</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>0.6435165382445049</v>
@@ -2645,10 +2629,8 @@
           <t>X &gt; 0.9303</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2270~2272</t>
-        </is>
+      <c r="B14" t="n">
+        <v>2270</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>1.24775886288861</v>
@@ -2699,10 +2681,8 @@
           <t>X &gt; 0.9902</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>1952~1952</t>
-        </is>
+      <c r="B15" t="n">
+        <v>1952</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>1.195086269953961</v>
@@ -2753,10 +2733,8 @@
           <t>X &gt; 1.05</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>1650~1650</t>
-        </is>
+      <c r="B16" t="n">
+        <v>1650</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>1.20353137675972</v>
@@ -2807,10 +2785,8 @@
           <t>X &gt; 1.11</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1352~1352</t>
-        </is>
+      <c r="B17" t="n">
+        <v>1352</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>0.9828930407367764</v>
@@ -2861,10 +2837,8 @@
           <t>X &gt; 1.17</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1134~1134</t>
-        </is>
+      <c r="B18" t="n">
+        <v>1134</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>1.915732755627772</v>
@@ -2915,10 +2889,8 @@
           <t>X &gt; 1.23</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>938~938</t>
-        </is>
+      <c r="B19" t="n">
+        <v>938</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>1.770954003883837</v>
@@ -2969,10 +2941,8 @@
           <t>X &gt; 1.289</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>764~764</t>
-        </is>
+      <c r="B20" t="n">
+        <v>764</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>1.433263250470645</v>
@@ -3023,10 +2993,8 @@
           <t>X &gt; 1.349</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>629~629</t>
-        </is>
+      <c r="B21" t="n">
+        <v>629</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>2.673493317309905</v>
@@ -3077,10 +3045,8 @@
           <t>X &gt; 1.409</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>548~548</t>
-        </is>
+      <c r="B22" t="n">
+        <v>548</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>3.345977738184189</v>
@@ -3131,10 +3097,8 @@
           <t>X &gt; 1.469</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>466~466</t>
-        </is>
+      <c r="B23" t="n">
+        <v>466</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>4.588106744167703</v>
@@ -3185,10 +3149,8 @@
           <t>X &gt; 1.529</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>392~392</t>
-        </is>
+      <c r="B24" t="n">
+        <v>392</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>4.649418822647164</v>
@@ -3239,10 +3201,8 @@
           <t>X &gt; 1.589</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>338~338</t>
-        </is>
+      <c r="B25" t="n">
+        <v>338</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>4.015437419434996</v>
@@ -3293,10 +3253,8 @@
           <t>X &gt; 1.649</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>289~289</t>
-        </is>
+      <c r="B26" t="n">
+        <v>289</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>3.907945762835006</v>
@@ -3347,10 +3305,8 @@
           <t>X &gt; 1.708</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>249~249</t>
-        </is>
+      <c r="B27" t="n">
+        <v>249</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>4.53467412958922</v>
@@ -3401,10 +3357,8 @@
           <t>X &gt; 1.768</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>212~212</t>
-        </is>
+      <c r="B28" t="n">
+        <v>212</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>4.582033377903237</v>
@@ -3455,10 +3409,8 @@
           <t>X &gt; 1.828</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>186~186</t>
-        </is>
+      <c r="B29" t="n">
+        <v>186</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>3.420540174413674</v>
@@ -3509,10 +3461,8 @@
           <t>X &gt; 1.888</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>156~156</t>
-        </is>
+      <c r="B30" t="n">
+        <v>156</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>1.352715525943871</v>
@@ -3563,10 +3513,8 @@
           <t>X &gt; 1.948</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>132~132</t>
-        </is>
+      <c r="B31" t="n">
+        <v>132</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>2.052016225244564</v>
@@ -3617,10 +3565,8 @@
           <t>X &gt; 2.008</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>117~117</t>
-        </is>
+      <c r="B32" t="n">
+        <v>117</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>1.352715525943871</v>
@@ -3671,10 +3617,8 @@
           <t>X &gt; 2.068</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>108~108</t>
-        </is>
+      <c r="B33" t="n">
+        <v>108</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>2.136191309419651</v>
@@ -3725,10 +3669,8 @@
           <t>X &gt; 2.127</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>93~93</t>
-        </is>
+      <c r="B34" t="n">
+        <v>93</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>2.345271357209377</v>
@@ -3779,10 +3721,8 @@
           <t>X &gt; 2.187</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+      <c r="B35" t="n">
+        <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>1.077990251218594</v>
@@ -3967,10 +3907,8 @@
           <t>X &lt; 0.4514</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+      <c r="B6" t="n">
+        <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>-6.064866891638545</v>
@@ -4021,10 +3959,8 @@
           <t>X &lt; 0.5113</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>165~167</t>
-        </is>
+      <c r="B7" t="n">
+        <v>165</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>-6.385653889072245</v>
@@ -4075,10 +4011,8 @@
           <t>X &lt; 0.5712</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>281~284</t>
-        </is>
+      <c r="B8" t="n">
+        <v>281</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>-1.789212968097303</v>
@@ -4129,10 +4063,8 @@
           <t>X &lt; 0.631</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>439~442</t>
-        </is>
+      <c r="B9" t="n">
+        <v>439</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>-1.588460944644368</v>
@@ -4183,10 +4115,8 @@
           <t>X &lt; 0.6909</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>644~649</t>
-        </is>
+      <c r="B10" t="n">
+        <v>644</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>-0.4133150536460235</v>
@@ -4237,10 +4167,8 @@
           <t>X &lt; 0.7507</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>894~900</t>
-        </is>
+      <c r="B11" t="n">
+        <v>894</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>-0.1601049868766466</v>
@@ -4291,10 +4219,8 @@
           <t>X &lt; 0.8106</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>1210~1218</t>
-        </is>
+      <c r="B12" t="n">
+        <v>1210</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>-1.672420257812604</v>
@@ -4345,10 +4271,8 @@
           <t>X &lt; 0.8704</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>1538~1548</t>
-        </is>
+      <c r="B13" t="n">
+        <v>1538</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>-1.007650206514889</v>
@@ -4399,10 +4323,8 @@
           <t>X &lt; 0.9303</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>1879~1890</t>
-        </is>
+      <c r="B14" t="n">
+        <v>1879</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>-1.435237262008918</v>
@@ -4453,10 +4375,8 @@
           <t>X &lt; 0.9902</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2197~2210</t>
-        </is>
+      <c r="B15" t="n">
+        <v>2197</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>-1.000225650526723</v>
@@ -4507,10 +4427,8 @@
           <t>X &lt; 1.05</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2499~2512</t>
-        </is>
+      <c r="B16" t="n">
+        <v>2499</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>-0.7418459635220742</v>
@@ -4561,10 +4479,8 @@
           <t>X &lt; 1.11</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2797~2810</t>
-        </is>
+      <c r="B17" t="n">
+        <v>2797</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>-0.4293813807081932</v>
@@ -4615,10 +4531,8 @@
           <t>X &lt; 1.17</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>3015~3028</t>
-        </is>
+      <c r="B18" t="n">
+        <v>3015</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>-0.6770578710686195</v>
@@ -4669,10 +4583,8 @@
           <t>X &lt; 1.23</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>3211~3224</t>
-        </is>
+      <c r="B19" t="n">
+        <v>3211</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>-0.4773092879519112</v>
@@ -4723,10 +4635,8 @@
           <t>X &lt; 1.289</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>3385~3398</t>
-        </is>
+      <c r="B20" t="n">
+        <v>3385</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>-0.2862576256837883</v>
@@ -4777,10 +4687,8 @@
           <t>X &lt; 1.349</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>3520~3533</t>
-        </is>
+      <c r="B21" t="n">
+        <v>3520</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>-0.4413579352679946</v>
@@ -4831,10 +4739,8 @@
           <t>X &lt; 1.409</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>3601~3614</t>
-        </is>
+      <c r="B22" t="n">
+        <v>3601</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>-0.4735157966903287</v>
@@ -4885,10 +4791,8 @@
           <t>X &lt; 1.469</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>3683~3696</t>
-        </is>
+      <c r="B23" t="n">
+        <v>3683</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>-0.5453863721580348</v>
@@ -4939,10 +4843,8 @@
           <t>X &lt; 1.529</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>3757~3770</t>
-        </is>
+      <c r="B24" t="n">
+        <v>3757</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>-0.4509980019075925</v>
@@ -4993,10 +4895,8 @@
           <t>X &lt; 1.589</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>3811~3824</t>
-        </is>
+      <c r="B25" t="n">
+        <v>3811</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>-0.3229362281597687</v>
@@ -5047,10 +4947,8 @@
           <t>X &lt; 1.649</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>3860~3873</t>
-        </is>
+      <c r="B26" t="n">
+        <v>3860</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>-0.2600275275427961</v>
@@ -5101,10 +4999,8 @@
           <t>X &lt; 1.708</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>3900~3913</t>
-        </is>
+      <c r="B27" t="n">
+        <v>3900</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>-0.2573023631437863</v>
@@ -5155,10 +5051,8 @@
           <t>X &lt; 1.768</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>3937~3950</t>
-        </is>
+      <c r="B28" t="n">
+        <v>3937</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>-0.2149573075517495</v>
@@ -5209,10 +5103,8 @@
           <t>X &lt; 1.828</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>3963~3976</t>
-        </is>
+      <c r="B29" t="n">
+        <v>3963</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>-0.1292532095459933</v>
@@ -5263,10 +5155,8 @@
           <t>X &lt; 1.888</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>3993~4006</t>
-        </is>
+      <c r="B30" t="n">
+        <v>3993</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>-0.02214525980058824</v>
@@ -5317,10 +5207,8 @@
           <t>X &lt; 1.948</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>4017~4030</t>
-        </is>
+      <c r="B31" t="n">
+        <v>4017</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>-0.03686263782783783</v>
@@ -5371,10 +5259,8 @@
           <t>X &lt; 2.008</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>4032~4045</t>
-        </is>
+      <c r="B32" t="n">
+        <v>4032</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>-0.008889494499221939</v>
@@ -5425,10 +5311,8 @@
           <t>X &lt; 2.068</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>4041~4054</t>
-        </is>
+      <c r="B33" t="n">
+        <v>4041</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>-0.02673876421589938</v>
@@ -5479,10 +5363,8 @@
           <t>X &lt; 2.127</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>4056~4069</t>
-        </is>
+      <c r="B34" t="n">
+        <v>4056</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>-0.02354399728050538</v>
@@ -5533,10 +5415,8 @@
           <t>X &lt; 2.187</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>4065~4078</t>
-        </is>
+      <c r="B35" t="n">
+        <v>4065</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>0.007787771011209088</v>

--- a/workspaces/btc_daily_14days/volume/volume_ratio_30.xlsx
+++ b/workspaces/btc_daily_14days/volume/volume_ratio_30.xlsx
@@ -479,7 +479,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that Volume Ratio-30 is approximately at value x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that Volume Ratio-30 is approximately at value x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -575,98 +575,98 @@
         <v>81</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-6.860447769541366</v>
+        <v>-6.84764803907175</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>1.341933137180085</v>
+        <v>1.355138193032182</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>10.23234882425942</v>
+        <v>9.5751802308123</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>6.671121319756963</v>
+        <v>6.684238739161962</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>11.05776351825644</v>
+        <v>11.07101905611272</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>6.431318755719218</v>
+        <v>6.444506373257752</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>5.113722467061358</v>
+        <v>5.126936381488783</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>3.409983895612832</v>
+        <v>3.423316351482669</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>3.349930674361104</v>
+        <v>3.363284105857964</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>6.19171099961985</v>
+        <v>6.205277048938939</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>2.978551042169414</v>
+        <v>2.29952686586153</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>1.779773275109129</v>
+        <v>1.793218855122348</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>1.360076412764144</v>
+        <v>1.373629049260117</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>1.610138940600095</v>
+        <v>1.599709304901943</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ 0.5413</t>
+          <t>X ≈ 0.5412</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>116</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>4.798451390321624</v>
+        <v>4.811056216134148</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>4.0389048215931</v>
+        <v>4.051902251435536</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>1.922800040147926</v>
+        <v>1.93632191644879</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-3.499414948883754</v>
+        <v>-3.954992642808804</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-8.339383831156169</v>
+        <v>-8.326305694252625</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-2.8813229035745</v>
+        <v>-2.868306023719107</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>1.33717130484581</v>
+        <v>1.350216821819139</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.8709162439815259</v>
+        <v>0.884079658028007</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-2.634600526521957</v>
+        <v>-2.621416784797688</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.8222133732009453</v>
+        <v>0.8356077977852721</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>4.063160709489587</v>
+        <v>4.07770619673817</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.652170898914747</v>
+        <v>0.6656159987237231</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-3.215173614085153</v>
+        <v>-3.201621452321071</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-2.966276555355641</v>
+        <v>-2.976706191053395</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>158</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-1.223878477693411</v>
+        <v>-1.211393673480153</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>4.112943066830617</v>
+        <v>4.125821759827886</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>1.824496905755318</v>
+        <v>1.83803030145345</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.6922402296392747</v>
+        <v>0.7053775278642505</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.1551173364659348</v>
+        <v>0.1681976553935627</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>4.87395749822317</v>
+        <v>4.886976294175483</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.9992919499159925</v>
+        <v>1.012335830381154</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>1.797133528857231</v>
+        <v>1.810296002153535</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>3.001164996670745</v>
+        <v>3.014349213883925</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>1.51998320983877</v>
+        <v>1.533377010434201</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>2.580050793412511</v>
+        <v>2.594276888508382</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>2.615293669085233</v>
+        <v>2.628738530606533</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>2.828653222351193</v>
+        <v>2.842205519840753</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>2.446207076246289</v>
+        <v>2.435777440547845</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>205</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>2.109909747649859</v>
+        <v>2.122538910394603</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-1.458144216329131</v>
+        <v>-1.445122813525145</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.5786515158426582</v>
+        <v>0.5918839667602924</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.2660098403157107</v>
+        <v>-0.2531295576416071</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.05410623586028862</v>
+        <v>-0.308766516177613</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.241938936005937</v>
+        <v>-0.2288497814917179</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>1.620950949052556</v>
+        <v>1.634068577643305</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-1.283673424337927</v>
+        <v>-1.270437442733382</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>1.091741354703146</v>
+        <v>1.105000056303538</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>3.435467016706994</v>
+        <v>3.177379015663583</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>2.743302947018719</v>
+        <v>2.757655240989884</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>3.266208048944868</v>
+        <v>3.279652290504544</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>1.871763664687684</v>
+        <v>1.885315518264385</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.8047963198635131</v>
+        <v>-0.8152259555617718</v>
       </c>
     </row>
     <row r="10">
@@ -783,150 +783,150 @@
         <v>250</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.4953171178992051</v>
+        <v>0.5078672976911562</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>3.272668586028615</v>
+        <v>3.285613405461419</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.4817866311237395</v>
+        <v>0.4950208195181744</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.1869786627754664</v>
+        <v>-0.1740879192706899</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.07196355791086972</v>
+        <v>0.085064722580384</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.3707587048359855</v>
+        <v>0.3838400021639785</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>1.883863613220527</v>
+        <v>1.896973655243464</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>1.635513426140825</v>
+        <v>1.428633084083174</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>2.374176602357196</v>
+        <v>2.38736159167437</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.7253392918220243</v>
+        <v>0.7390816649394978</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.9202176433792815</v>
+        <v>0.9341349572624864</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.9551578395386997</v>
+        <v>0.9686006058467385</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>2.135020825691754</v>
+        <v>2.148572141891393</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>3.985447582575304</v>
+        <v>3.975017946877244</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ 0.7807</t>
+          <t>X ≈ 0.7806</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-5.980435915790338</v>
+        <v>-5.946720422941162</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-1.911622402382164</v>
+        <v>-1.893121271870619</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-1.044366623958375</v>
+        <v>-1.029055648531632</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.2835837462402679</v>
+        <v>-0.2693224486170109</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>2.335664454006505</v>
+        <v>2.341740830216679</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>2.320895199925658</v>
+        <v>2.325184718186833</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>1.288200670306239</v>
+        <v>1.295888905009505</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.8173799548514538</v>
+        <v>0.8277166140046504</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.1249919745385597</v>
+        <v>0.1367038591870653</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-2.311099928108796</v>
+        <v>-2.291844977534588</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-1.250277261907044</v>
+        <v>-1.235059324037607</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-1.673225813244699</v>
+        <v>-1.83181316389971</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-1.46277622225395</v>
+        <v>-1.445294724893955</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-1.98417267058916</v>
+        <v>-1.850849561009184</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ 0.8405</t>
+          <t>X ≈ 0.8404</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>328</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1.449477392307642</v>
+        <v>1.461808262329669</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-2.742147052065626</v>
+        <v>-2.893465608800291</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-3.746652370056907</v>
+        <v>-3.733645238639305</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-2.094274316517875</v>
+        <v>-2.081295174119411</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-1.719562432690992</v>
+        <v>-1.706451628316053</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-2.944520086234093</v>
+        <v>-2.930493251313806</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-4.859092399142803</v>
+        <v>-4.844288314353768</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-3.499610593952163</v>
+        <v>-3.486429584656925</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-2.03713337693349</v>
+        <v>-2.023242677862086</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-4.719430455108807</v>
+        <v>-4.706025327455976</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-4.313909181782542</v>
+        <v>-4.300451888072324</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-3.975373875772682</v>
+        <v>-3.961921587052572</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-3.005737164335031</v>
+        <v>-3.164219445509552</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.9267475393758176</v>
+        <v>-0.9371771750739697</v>
       </c>
     </row>
     <row r="13">
@@ -936,101 +936,101 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-3.378859053961065</v>
+        <v>-3.378067299386892</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-2.355812161604547</v>
+        <v>-2.190840293470437</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-5.095519278293708</v>
+        <v>-5.231207690659247</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-4.672504396669801</v>
+        <v>-4.807359961897141</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.06270646763957188</v>
+        <v>-0.0565051583527918</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.5207651657421692</v>
+        <v>0.2419714618662425</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.7296146530303176</v>
+        <v>0.6114111874133386</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.3235678767647485</v>
+        <v>-0.4431558376440776</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-3.317365428984722</v>
+        <v>-3.444171589351143</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.0619187665051868</v>
+        <v>-0.1778909029546014</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.439692618682002</v>
+        <v>-1.559062649449956</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-1.991819725266325</v>
+        <v>-2.112919791212349</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>1.400242379331438</v>
+        <v>1.290458767238889</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-1.869097871970062</v>
+        <v>-2.013217347240406</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ 0.9603</t>
+          <t>X ≈ 0.9602</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>1.571082452223266</v>
+        <v>1.414271719349451</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-3.190958429763903</v>
+        <v>-3.337503020318209</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-1.075363410609761</v>
+        <v>-0.9164743700429909</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-1.260129323090311</v>
+        <v>-1.100280508217878</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-1.165744266570556</v>
+        <v>-1.007749208091887</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-2.122288510093462</v>
+        <v>-1.960432068181895</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-3.924062506616451</v>
+        <v>-3.928226802150668</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-5.022530713298508</v>
+        <v>-4.853110165771653</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-5.537989195560947</v>
+        <v>-5.54118954513001</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-7.017045198199007</v>
+        <v>-6.84394290369206</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-5.649471478491421</v>
+        <v>-5.481245942830142</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-5.300622912340891</v>
+        <v>-5.133388166650363</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-5.720877523285864</v>
+        <v>-5.553539019963637</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-2.955432920569258</v>
+        <v>-2.819966379141562</v>
       </c>
     </row>
     <row r="15">
@@ -1043,46 +1043,46 @@
         <v>302</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>1.148945785750286</v>
+        <v>1.161468075425908</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.1996238284151701</v>
+        <v>0.2125336379912213</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.1952448781813416</v>
+        <v>-0.1822377467637395</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-1.720620884646841</v>
+        <v>-1.707641742248377</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-1.596790444089869</v>
+        <v>-1.58367963971493</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1.018532288327968</v>
+        <v>1.031575184622334</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.05957891238805502</v>
+        <v>-0.04651265808757898</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.4666151722740679</v>
+        <v>0.4797961815693057</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>2.392370252979305</v>
+        <v>2.405568991934068</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.1133840711215939</v>
+        <v>-0.09997894346876279</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.01298843237540126</v>
+        <v>0.02644572608561901</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.378497417535371</v>
+        <v>0.3919497062554811</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.7040088490385941</v>
+        <v>-0.6904528026869912</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>1.863593277939636</v>
+        <v>1.853163642241483</v>
       </c>
     </row>
     <row r="16">
@@ -1095,46 +1095,46 @@
         <v>298</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>2.204548256971194</v>
+        <v>2.217070546646816</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-3.098300523778256</v>
+        <v>-3.085390714202205</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-3.493169230374846</v>
+        <v>-3.480162098957244</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.3283590700178891</v>
+        <v>0.3413382124163533</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-3.230196373242201</v>
+        <v>-3.217085568867262</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-3.939465844922594</v>
+        <v>-3.926422948628229</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-3.688629092396134</v>
+        <v>-3.675562838095658</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-1.806819202586993</v>
+        <v>-1.793638193291756</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.8611076793733972</v>
+        <v>-0.847908940418634</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-1.040091924803974</v>
+        <v>-1.026686797151143</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-1.580415718920207</v>
+        <v>-1.56695842520999</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.467390257217204</v>
+        <v>0.480842545937314</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.04713564627222411</v>
+        <v>0.06069169262382701</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.7098544308474217</v>
+        <v>-0.7202840665455739</v>
       </c>
     </row>
     <row r="17">
@@ -1144,49 +1144,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-3.869585109200798</v>
+        <v>-4.093819256340694</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.0234284337981947</v>
+        <v>-0.1750514323538894</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.5459909198622057</v>
+        <v>0.3518361690660825</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.2175284561394832</v>
+        <v>0.02123181956693543</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-1.238323951593344</v>
+        <v>-1.438716719703812</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-5.069322380850053</v>
+        <v>-5.288808127856747</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-3.777909309131608</v>
+        <v>-3.991030007860253</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-3.786377111582894</v>
+        <v>-3.997269158559575</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-5.223523786755912</v>
+        <v>-5.440739794344928</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-4.697502182793009</v>
+        <v>-4.908170111412112</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-6.278402296101419</v>
+        <v>-6.49535974893498</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-6.244019138755988</v>
+        <v>-6.460981596579657</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-7.122989346031162</v>
+        <v>-6.881132449893066</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-5.95583682109433</v>
+        <v>-5.733737813491373</v>
       </c>
     </row>
     <row r="18">
@@ -1196,101 +1196,101 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>2.608602496116639</v>
+        <v>2.849033208044297</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>3.548049291315621</v>
+        <v>3.775918180970287</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>2.642976503086317</v>
+        <v>2.873532583017401</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>6.344658207122279</v>
+        <v>6.557057218991424</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>3.76542066551967</v>
+        <v>3.988310813103858</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>3.042454439969966</v>
+        <v>3.270456416343059</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>4.488332967595646</v>
+        <v>4.708588696670695</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>5.551761813712169</v>
+        <v>5.764362692478031</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>3.960149682631844</v>
+        <v>4.180537896361287</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>6.171248987399835</v>
+        <v>6.376304379219242</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>6.476699744714963</v>
+        <v>6.679217434157081</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>7.021286983692995</v>
+        <v>7.221209799710316</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>2.51939971968681</v>
+        <v>2.232531027615124</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>2.258916970330503</v>
+        <v>1.950652464643689</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ 1.26</t>
+          <t>X ≈ 1.259</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>174</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>3.253688116571638</v>
+        <v>3.266210406247261</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>4.515677721998209</v>
+        <v>4.52858753157426</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>3.546096371723429</v>
+        <v>3.559103503141031</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-2.645489576128739</v>
+        <v>-2.632510433730275</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-3.183910791201008</v>
+        <v>-3.170799986826069</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-5.760032071876182</v>
+        <v>-5.746989175581817</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-4.120627858113892</v>
+        <v>-4.107561603813416</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.5846025362080027</v>
+        <v>0.5977835455032405</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-2.349960568365105</v>
+        <v>-2.336761829410342</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.8229027523540964</v>
+        <v>0.8363078800069275</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-2.830126434032522</v>
+        <v>-2.816669140322304</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.0778199417037797</v>
+        <v>0.09127223042388977</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1.956415905471587</v>
+        <v>1.96997195182319</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1.631424594069649</v>
+        <v>1.620994958371497</v>
       </c>
     </row>
     <row r="20">
@@ -1303,46 +1303,46 @@
         <v>135</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-4.345290172061915</v>
+        <v>-4.332767882386293</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-3.734641562803901</v>
+        <v>-3.72173175322785</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.166547306437486</v>
+        <v>-1.153540175019884</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>4.889631752095902</v>
+        <v>4.902610894494366</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>3.61046979628302</v>
+        <v>3.623580600657959</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>7.61161543770244</v>
+        <v>7.624658333996805</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>6.045400238948631</v>
+        <v>6.058466493249107</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>6.31895758090787</v>
+        <v>6.332138590203108</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>6.998698435466309</v>
+        <v>7.011897174421073</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>6.889313991179122</v>
+        <v>6.902719118831953</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>3.721597703898581</v>
+        <v>3.735054997608799</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>4.496721601984753</v>
+        <v>4.510173890704863</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>4.817207731780591</v>
+        <v>4.830763778132194</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>3.585447582575398</v>
+        <v>3.575017946877246</v>
       </c>
     </row>
     <row r="21">
@@ -1352,49 +1352,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.87615436959269</v>
+        <v>-1.23091603053421</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>3.919679424850528</v>
+        <v>3.407897876401812</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>3.524810718253875</v>
+        <v>3.013126491646851</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>1.185928048392235</v>
+        <v>0.6433516352350708</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>3.116642635789127</v>
+        <v>2.60506208213944</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>3.414084573504866</v>
+        <v>2.902436111774527</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>4.563918757467142</v>
+        <v>5.317725752508295</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>5.331303259920141</v>
+        <v>4.850657108721627</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>8.974007077441549</v>
+        <v>8.539674952198844</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>11.8275855961174</v>
+        <v>11.43975615586892</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>9.153696469330683</v>
+        <v>8.73505499760887</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>7.953511725441544</v>
+        <v>7.519433149964051</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>6.298689213262072</v>
+        <v>5.849282296650777</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>7.78297844677293</v>
+        <v>7.325017946877175</v>
       </c>
     </row>
     <row r="22">
@@ -1404,49 +1404,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-3.712950515331855</v>
+        <v>-4.288144946197072</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-2.885499738052282</v>
+        <v>-2.284873207935462</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-3.280368444648872</v>
+        <v>-2.679644592690636</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-4.369627507163386</v>
+        <v>-3.754238726210644</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-4.908048722235357</v>
+        <v>-4.292528279306275</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-2.171582394275859</v>
+        <v>-1.585515695454312</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>2.621732668939593</v>
+        <v>1.944231776604823</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.9350370750362202</v>
+        <v>1.477163132818021</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-2.78449939651194</v>
+        <v>-2.198276855030059</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>2.462936394069814</v>
+        <v>2.975900734182311</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>2.258183069752171</v>
+        <v>2.771199575921919</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>4.731590617341574</v>
+        <v>5.21521628249431</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>5.530848201518623</v>
+        <v>5.999884706289201</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>5.780569533794974</v>
+        <v>6.225620356515932</v>
       </c>
     </row>
     <row r="23">
@@ -1459,46 +1459,46 @@
         <v>74</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>4.263318436546783</v>
+        <v>4.275840726222405</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-4.10501193317431</v>
+        <v>-4.092102123598259</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-1.797177937068128</v>
+        <v>-1.784170805650525</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1.035777898242159</v>
+        <v>1.048757040640623</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-4.90804872223557</v>
+        <v>-4.894937917860631</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.5565527304658531</v>
+        <v>-0.5435098341714877</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-6.046691853143457</v>
+        <v>-6.033625598842981</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-6.513875251924958</v>
+        <v>-6.50069424262972</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-5.223523786755948</v>
+        <v>-5.210325047801184</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-4.722297620432492</v>
+        <v>-4.708892492779661</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-7.629753647452695</v>
+        <v>-7.616296353742477</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-2.189965084701932</v>
+        <v>-2.176512795981822</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-2.610219695646876</v>
+        <v>-2.596663649295273</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-5.063201066073333</v>
+        <v>-5.073630701771485</v>
       </c>
     </row>
     <row r="24">
@@ -1511,46 +1511,46 @@
         <v>54</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>8.617672790901139</v>
+        <v>8.630195080576762</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.4013082294705228</v>
+        <v>-0.3883984198944717</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>2.907526767636583</v>
+        <v>2.920533899054185</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-4.369627507163372</v>
+        <v>-4.356648364764908</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.6475068333200653</v>
+        <v>0.6606176376950046</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-2.758754932667983</v>
+        <v>-2.745712036373618</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.8602150537634472</v>
+        <v>0.8732813080639232</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>2.244883506833794</v>
+        <v>2.258064516129032</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.3320317687997019</v>
+        <v>0.3452305077544651</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-2.36994526808013</v>
+        <v>-2.356540140427299</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.7228467405458616</v>
+        <v>-0.7093894468356439</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-2.540315435052278</v>
+        <v>-2.526863146332168</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-4.812421897848985</v>
+        <v>-4.798865851497382</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-6.414552417424602</v>
+        <v>-6.424982053122754</v>
       </c>
     </row>
     <row r="25">
@@ -1563,98 +1563,98 @@
         <v>49</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>4.649418822647164</v>
+        <v>4.661941112322786</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>17.3235594953972</v>
+        <v>17.33646930497325</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>14.88787446226999</v>
+        <v>14.90088159368759</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>17.05894392140817</v>
+        <v>17.07192306380663</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>10.3980737267441</v>
+        <v>10.41118453111904</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>4.573066684867925</v>
+        <v>4.58610958116229</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>10.61078194718748</v>
+        <v>10.62384820148796</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>8.102782221875373</v>
+        <v>8.11596323117061</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>10.08259866222368</v>
+        <v>10.09579740117844</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>3.110024497603916</v>
+        <v>3.123429625256747</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>6.986903826347564</v>
+        <v>7.000361120057782</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>9.062103310223605</v>
+        <v>9.075555598943716</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>10.68266502580936</v>
+        <v>10.69622107216097</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>6.850753705024381</v>
+        <v>6.840324069326229</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 1.679</t>
+          <t>X ≈ 1.678</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>40</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.006561679790024755</v>
+        <v>0.0190839694656475</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.8949880668257748</v>
+        <v>0.907897876401826</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>5.500119360229107</v>
+        <v>5.513126491646709</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.6303724928366066</v>
+        <v>0.6433516352350708</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-2.408048722235492</v>
+        <v>-2.394937917860553</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-7.110606784519902</v>
+        <v>-7.097563888225537</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-7.19534050179211</v>
+        <v>-7.182274247491634</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-12.66252390057368</v>
+        <v>-12.64934289127844</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-17.72352378675584</v>
+        <v>-17.71032504780108</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-13.57364897178384</v>
+        <v>-13.56024384413101</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-11.27840229610142</v>
+        <v>-11.2649450023912</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-13.74401913875599</v>
+        <v>-13.73056685003588</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-11.66427374970096</v>
+        <v>-11.65071770334936</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-6.414552417424673</v>
+        <v>-6.424982053122825</v>
       </c>
     </row>
     <row r="27">
@@ -1667,46 +1667,46 @@
         <v>37</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>4.263318436546747</v>
+        <v>4.27584072622237</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>8.057150228987929</v>
+        <v>8.07006003856398</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>2.256876116986007</v>
+        <v>2.269883248403609</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>7.792534654998839</v>
+        <v>7.805513797397303</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.8539946681814357</v>
+        <v>-0.8408838638064964</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>4.848852674939707</v>
+        <v>4.861895571234072</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>10.16952436307276</v>
+        <v>10.18259061737324</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>6.999638261588551</v>
+        <v>7.012819270883789</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>4.235935672703469</v>
+        <v>4.249134411658233</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-2.019594917729783</v>
+        <v>-2.006189790076952</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-2.224348242047284</v>
+        <v>-2.210890948337067</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>5.918143023406174</v>
+        <v>5.931595312126284</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>8.200591115163981</v>
+        <v>8.214147161515584</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>11.15301515014305</v>
+        <v>11.1425855144449</v>
       </c>
     </row>
     <row r="28">
@@ -1719,46 +1719,46 @@
         <v>26</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>12.89117706440553</v>
+        <v>12.90369935408115</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.2588580870203856</v>
+        <v>-0.2459482774443345</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>3.192427052536864</v>
+        <v>3.205434183954466</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.5234736610093691</v>
+        <v>-0.5104945186109049</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>6.630412816226048</v>
+        <v>6.643523620600988</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>6.927854753941709</v>
+        <v>6.940897650236074</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>6.84312103666943</v>
+        <v>6.856187290969906</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>6.375937637888043</v>
+        <v>6.389118647183281</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>14.00724544401331</v>
+        <v>14.02044418296808</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>20.84942795129309</v>
+        <v>20.86283307894593</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>24.4908284731293</v>
+        <v>24.50428576683952</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>12.98675009201324</v>
+        <v>13.00020238073335</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>12.56649548106834</v>
+        <v>12.58005152741994</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>12.81621681334457</v>
+        <v>12.80578717764642</v>
       </c>
     </row>
     <row r="29">
@@ -1771,46 +1771,46 @@
         <v>30</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>14.17322834645664</v>
+        <v>14.18575063613226</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-4.105011933174232</v>
+        <v>-4.092102123598181</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>8.833452693562506</v>
+        <v>8.846459824980109</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>5.630372492836678</v>
+        <v>5.643351635235142</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-1.574715388902206</v>
+        <v>-1.561604584527267</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>2.056059882146833</v>
+        <v>2.069102778441199</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>1.971326164874554</v>
+        <v>1.98439241917503</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>4.837476099426432</v>
+        <v>4.85065710872167</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>4.776476213244088</v>
+        <v>4.789674952198851</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>3.92635102821616</v>
+        <v>3.939756155868992</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>3.721597703898532</v>
+        <v>3.735054997608749</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-6.244019138755945</v>
+        <v>-6.230566850035835</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-6.664273749700889</v>
+        <v>-6.650717703349287</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-6.414552417424559</v>
+        <v>-6.424982053122712</v>
       </c>
     </row>
     <row r="30">
@@ -1823,46 +1823,46 @@
         <v>24</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-2.493438320209918</v>
+        <v>-2.480916030534296</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.061654733492432</v>
+        <v>0.07456454306848315</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.3332139731041579</v>
+        <v>-0.3202068416865558</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.2029608404966581</v>
+        <v>-0.1899816980981939</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>7.591951277764565</v>
+        <v>7.605062082139504</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.4439401178531668</v>
+        <v>-0.4308972215588014</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.5286738351254456</v>
+        <v>-0.5156075808249696</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.9958572339070031</v>
+        <v>-0.9826762246117653</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>7.276476213244088</v>
+        <v>7.289674952198851</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-6.073648971783783</v>
+        <v>-6.060243844130952</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>6.221597703898638</v>
+        <v>6.235054997608856</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>2.089314194577284</v>
+        <v>2.102766483297394</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>1.669059583632446</v>
+        <v>1.682615629984049</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-2.247885750757938</v>
+        <v>-2.25831538645609</v>
       </c>
     </row>
     <row r="31">
@@ -1875,150 +1875,150 @@
         <v>15</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>7.506561679789932</v>
+        <v>7.519083969465555</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>12.56165473349242</v>
+        <v>12.57456454306848</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-1.166547306437486</v>
+        <v>-1.153540175019884</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>5.630372492836678</v>
+        <v>5.643351635235142</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>18.42528461109784</v>
+        <v>18.43839541547278</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>5.389393215480169</v>
+        <v>5.402436111774534</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>18.63799283154132</v>
+        <v>18.65105908584179</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>11.50414276609305</v>
+        <v>11.51732377538828</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>4.776476213244088</v>
+        <v>4.789674952198851</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>3.926351028216068</v>
+        <v>3.939756155868899</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-2.945068962768175</v>
+        <v>-2.931611669057958</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>10.42264752791067</v>
+        <v>10.43609981663078</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>3.335726250299111</v>
+        <v>3.349282296650713</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>10.25211424924206</v>
+        <v>10.2416846135439</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X ≈ 2.038</t>
+          <t>X ≈ 2.037</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>9</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-8.048993875765532</v>
+        <v>-8.03647158608991</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-20.77167859984074</v>
+        <v>-20.75876879026469</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-21.16654730643749</v>
+        <v>-21.15354017501989</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>1.185928048392391</v>
+        <v>1.198907190790855</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.6475068333202216</v>
+        <v>0.6606176376951609</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.9449487710358824</v>
+        <v>0.9579916673302478</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-10.25089605734767</v>
+        <v>-10.23782980304719</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-10.71807945612917</v>
+        <v>-10.70489844683393</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0.3320317687998013</v>
+        <v>0.3452305077545645</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.5180934162282824</v>
+        <v>-0.5046882885754513</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>10.38826437056524</v>
+        <v>10.40172166427546</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>10.42264752791067</v>
+        <v>10.43609981663078</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-1.108718194145176</v>
+        <v>-1.095162147793573</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>10.25211424924206</v>
+        <v>10.2416846135439</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ 2.098</t>
+          <t>X ≈ 2.097</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>15</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.8398950131233605</v>
+        <v>0.8524173027989832</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>12.56165473349238</v>
+        <v>12.57456454306843</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>12.16678602689589</v>
+        <v>12.17979315831349</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-1.036294173830036</v>
+        <v>-1.023315031431572</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>18.42528461109775</v>
+        <v>18.43839541547269</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>18.72272654881341</v>
+        <v>18.73576944510778</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>18.63799283154113</v>
+        <v>18.65105908584161</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>24.83747609942639</v>
+        <v>24.85065710872163</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>11.44314287991066</v>
+        <v>11.45634161886542</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>17.25968436154955</v>
+        <v>17.27308948920238</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>10.38826437056515</v>
+        <v>10.40172166427537</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>10.42264752791067</v>
+        <v>10.43609981663078</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>16.66905958363235</v>
+        <v>16.68261562998396</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>10.25211424924206</v>
+        <v>10.2416846135439</v>
       </c>
     </row>
     <row r="34">
@@ -2031,46 +2031,46 @@
         <v>9</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>14.17322834645668</v>
+        <v>14.1857506361323</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>12.56165473349242</v>
+        <v>12.57456454306848</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>34.38900824911798</v>
+        <v>34.40201538053558</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>12.29703915950333</v>
+        <v>12.3100183019018</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>11.75861794443117</v>
+        <v>11.7717287488061</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>23.16717099325795</v>
+        <v>23.18021388955232</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.860215053763369</v>
+        <v>0.8732813080638451</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>11.50414276609305</v>
+        <v>11.51732377538828</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>11.44314287991067</v>
+        <v>11.45634161886544</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>21.70412880599395</v>
+        <v>21.71753393364678</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>21.49937548167651</v>
+        <v>21.51283277538673</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>10.42264752791067</v>
+        <v>10.43609981663078</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>21.1135040280769</v>
+        <v>21.1270600744285</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>21.36322536035318</v>
+        <v>21.35279572465503</v>
       </c>
     </row>
   </sheetData>
@@ -2121,7 +2121,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that Volume Ratio-30 is above threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that Volume Ratio-30 is above threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -2210,53 +2210,53 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; 0.4514</t>
+          <t>X &gt; 0.4515</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4065</v>
+        <v>4066</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.1549187175536275</v>
+        <v>0.1545338346286798</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.1750959893177964</v>
+        <v>0.1746953261320812</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.1370182807394826</v>
+        <v>0.1366241615020627</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.1334399774992576</v>
+        <v>0.1330474154117809</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.07476914718031935</v>
+        <v>0.07438723551368298</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.09108729846568764</v>
+        <v>0.09070317117561899</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.1671349402511169</v>
+        <v>0.1667313994516491</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.131015770268931</v>
+        <v>0.1306178159907887</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.05903149579936695</v>
+        <v>0.05865063384955249</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.05807872543906001</v>
+        <v>0.05769227380510955</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.08371203061469146</v>
+        <v>-0.08406517933885738</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.01092349085827493</v>
+        <v>-0.01129448032103397</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.0007533039144576037</v>
+        <v>0.0003764692595211727</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.09221265022607383</v>
+        <v>0.09247982587380221</v>
       </c>
     </row>
     <row r="7">
@@ -2266,101 +2266,101 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3984</v>
+        <v>3985</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.2975504157099209</v>
+        <v>0.2968617472434261</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.1513726436910687</v>
+        <v>0.1507013807822943</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.06823316856400652</v>
+        <v>-0.05522603714640439</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.0005202514141942061</v>
+        <v>-0.0001135625615518165</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.1485296841593353</v>
+        <v>-0.1491327588322449</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.03781800977665739</v>
+        <v>-0.03844565175251802</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.06656426011265637</v>
+        <v>0.06590916518689482</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.06435000266028368</v>
+        <v>0.06368969017526638</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.007876845933438403</v>
+        <v>-0.00852008415111527</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.06662614760526253</v>
+        <v>-0.06726490732057755</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.145971897305337</v>
+        <v>-0.1325146035951192</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.04733072932297233</v>
+        <v>-0.04797342139278982</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.02688353640101582</v>
+        <v>-0.02753656938039484</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.06135119703323255</v>
+        <v>0.06184354286219218</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; 0.5712</t>
+          <t>X &gt; 0.5711</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3868</v>
+        <v>3869</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.1625699314661446</v>
+        <v>0.1615175863772222</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.03478688034137178</v>
+        <v>0.03373593725793</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.1279435750300379</v>
+        <v>-0.1149364436124358</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.1054821136775317</v>
+        <v>0.1184612560759959</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.09711123648483522</v>
+        <v>0.09603448348069321</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.04745773160920663</v>
+        <v>0.04639896007174826</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.0284591884505403</v>
+        <v>0.02740317186320596</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.0401613563331793</v>
+        <v>0.03909283407009667</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.07089770084739655</v>
+        <v>0.06981954295537207</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.09328214150742298</v>
+        <v>-0.09433475322191498</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.272202347767653</v>
+        <v>-0.2587450540574352</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.06830854444074674</v>
+        <v>-0.06936819335802369</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.06873219498766048</v>
+        <v>0.06762854988069478</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.1521487201141767</v>
+        <v>0.1529450598263224</v>
       </c>
     </row>
     <row r="9">
@@ -2370,101 +2370,101 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3710</v>
+        <v>3711</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.2216154432308812</v>
+        <v>0.2199708278370593</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.1388920084632872</v>
+        <v>-0.1404892203723733</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.2110933313545829</v>
+        <v>-0.1980861999369807</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.08049349310557119</v>
+        <v>0.0934726355040354</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.09464089583873658</v>
+        <v>0.09296205525050283</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.1580913150552092</v>
+        <v>-0.1596940657402612</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.0128862499083624</v>
+        <v>-0.01453144415560814</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.03466387365571677</v>
+        <v>-0.03631813347428903</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.05389535379952548</v>
+        <v>-0.05554712047947419</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.1619872427237823</v>
+        <v>-0.1636364127901331</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.393672966718178</v>
+        <v>-0.3802156730079602</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.1825967249628846</v>
+        <v>-0.1842431225917665</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.04880622073295626</v>
+        <v>-0.0505021861079058</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.05445027799319035</v>
+        <v>0.05575090295377549</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; 0.6909</t>
+          <t>X &gt; 0.6908</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3505</v>
+        <v>3506</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.1111731230009596</v>
+        <v>0.1087254037285916</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.06173175094188821</v>
+        <v>-0.06420573874193991</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.2572838288368828</v>
+        <v>-0.2442766974192807</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.1007597365724422</v>
+        <v>0.1137388789709064</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.1033407994045916</v>
+        <v>0.1164516037795309</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.1531872459268442</v>
+        <v>-0.155650448589931</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.1084459148975228</v>
+        <v>-0.1109270529601645</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.03838804015023811</v>
+        <v>0.0358422939068106</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.1209012097889826</v>
+        <v>-0.1234056975589155</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.3723946958431341</v>
+        <v>-0.358989568190303</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.5771480201607133</v>
+        <v>-0.5636907264504956</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.3843099856336636</v>
+        <v>-0.3867812171966492</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.1611362710927864</v>
+        <v>-0.1636917552454875</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.1047057851431532</v>
+        <v>0.1066779582862623</v>
       </c>
     </row>
     <row r="11">
@@ -2474,101 +2474,101 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3255</v>
+        <v>3256</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.08166897592735722</v>
+        <v>0.0780787595361403</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.3178300871147357</v>
+        <v>-0.3214092971113587</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.3140480730734865</v>
+        <v>-0.3010409416558844</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.1228594600246566</v>
+        <v>0.1358386024231208</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.1057507257865922</v>
+        <v>0.1188615301615314</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.1934288704094058</v>
+        <v>-0.1970732411846754</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.2614650798835498</v>
+        <v>-0.2650963333812086</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.08427904018698484</v>
+        <v>-0.07109803089174704</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.3125354503532094</v>
+        <v>-0.3161857412654001</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.456706062023251</v>
+        <v>-0.44330093437042</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.6921530634433495</v>
+        <v>-0.6786957697331317</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.487187698780545</v>
+        <v>-0.4908492318652193</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.3374924229195599</v>
+        <v>-0.3412304451362118</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.1933542607425736</v>
+        <v>-0.1903383184790215</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; 0.8106</t>
+          <t>X &gt; 0.8105</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>2939</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.7334638537030713</v>
+        <v>0.7279124923858546</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.1464662315092582</v>
+        <v>-0.151884732293837</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.2355245405523405</v>
+        <v>-0.2225174091347384</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.1665600565471834</v>
+        <v>0.1795391989456476</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.1340086270944809</v>
+        <v>-0.1208978227195416</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.4637678994076637</v>
+        <v>-0.469123521252989</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.4280844664299863</v>
+        <v>-0.4334639143849017</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.1812250226409375</v>
+        <v>-0.1680440133456997</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.3595782085246242</v>
+        <v>-0.3650343303580996</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.2573224411715884</v>
+        <v>-0.2439173135187573</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.632143792700063</v>
+        <v>-0.6186864989898453</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.3596653972593913</v>
+        <v>-0.3462131085392812</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.216502398901298</v>
+        <v>-0.222146274777856</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.0008062452572019652</v>
+        <v>-0.01123588095535411</v>
       </c>
     </row>
     <row r="13">
@@ -2581,150 +2581,150 @@
         <v>2611</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.6435165382445049</v>
+        <v>0.6357187687008334</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.1796093369099339</v>
+        <v>0.192519146485985</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.2055516479108874</v>
+        <v>0.2185587793284895</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.4505714216813672</v>
+        <v>0.4635505640798314</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.06517239482648307</v>
+        <v>0.07828319920142235</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.1521299379832755</v>
+        <v>-0.1599204299240142</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.1285492378709776</v>
+        <v>0.1206342867601791</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.2356384271446146</v>
+        <v>0.2488194364398524</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.1488397576482896</v>
+        <v>-0.1567262729160035</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.303218128943854</v>
+        <v>0.3166232565966851</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.1696317101190346</v>
+        <v>-0.1561744164088168</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.09454845986522287</v>
+        <v>0.1080007485853329</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.1338878741980025</v>
+        <v>0.1474439205496054</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.1155126917289806</v>
+        <v>0.1050830560308285</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; 0.9303</t>
+          <t>X &gt; 0.9302</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2270</v>
+        <v>2271</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>1.24775886288861</v>
+        <v>1.236637862998421</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.5604810245722405</v>
+        <v>0.5493409032385941</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1.001879923609465</v>
+        <v>1.034463931154036</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>1.220161225231038</v>
+        <v>1.252678516009453</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.06554282706028403</v>
+        <v>0.09846287404441512</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.2532124183226472</v>
+        <v>-0.2200891851898348</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.03825703233382427</v>
+        <v>0.04715822061218944</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.3196425459257242</v>
+        <v>0.3524176721019145</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.3271370061956347</v>
+        <v>0.3354496000861786</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.3580690898901651</v>
+        <v>0.3906588419103869</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.02115717526421435</v>
+        <v>0.05385728734899686</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.4079632400986384</v>
+        <v>0.4405031631741565</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.05634423428239188</v>
+        <v>-0.02368115557297301</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.4136414151745171</v>
+        <v>0.4222218218222054</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; 0.9902</t>
+          <t>X &gt; 0.9901</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>1952</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>1.195086269953961</v>
+        <v>1.207608559629584</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>1.17162741108806</v>
+        <v>1.184537220664112</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1.340283294655414</v>
+        <v>1.353290426073016</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1.624224951853066</v>
+        <v>1.63720409425153</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.2661316056333547</v>
+        <v>0.279242410008294</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.05127846138181269</v>
+        <v>0.06432135767617808</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.6837578588636362</v>
+        <v>0.6968241131641122</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>1.189935115819829</v>
+        <v>1.203116125115066</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>1.2826237542277</v>
+        <v>1.295822493182463</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>1.559547749527638</v>
+        <v>1.572952877180469</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.9449583596362885</v>
+        <v>0.9584156533465062</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>1.337948074358764</v>
+        <v>1.351400363078874</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.8664639552171423</v>
+        <v>0.8800200015687452</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.9624967629032639</v>
+        <v>0.9520671272051118</v>
       </c>
     </row>
     <row r="16">
@@ -2737,46 +2737,46 @@
         <v>1650</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1.20353137675972</v>
+        <v>1.216053666435343</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1.349533521371221</v>
+        <v>1.362443330947272</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1.621331481441295</v>
+        <v>1.634338612858897</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>2.23643309889728</v>
+        <v>2.249412241295744</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.6071027929160238</v>
+        <v>0.620213597290963</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.1257582996713538</v>
+        <v>-0.1127154033769884</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.8198110133594056</v>
+        <v>0.8328772676598817</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1.322324584274874</v>
+        <v>1.335505593570112</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>1.079506516274385</v>
+        <v>1.092705255229149</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>1.865744967610098</v>
+        <v>1.879150095262929</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>1.115537097837979</v>
+        <v>1.128994391548197</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>1.513556618819777</v>
+        <v>1.527008907539887</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>1.153908068480924</v>
+        <v>1.167464114832526</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.797568794696609</v>
+        <v>0.7871391589984569</v>
       </c>
     </row>
     <row r="17">
@@ -2789,46 +2789,46 @@
         <v>1352</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.9828930407367764</v>
+        <v>0.9954153304123992</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>2.329899309429315</v>
+        <v>2.342809119005366</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>2.748640070288346</v>
+        <v>2.761647201705948</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>2.65699971177159</v>
+        <v>2.669978854170054</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.45289802332664</v>
+        <v>1.466008827701579</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.7148370024624242</v>
+        <v>0.7278798987567896</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>1.813535237852861</v>
+        <v>1.826601492153337</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>2.012032312444134</v>
+        <v>2.025213321739372</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>1.507245444013314</v>
+        <v>1.520444182968077</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>2.50623268502089</v>
+        <v>2.519637812673722</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>1.709763384371954</v>
+        <v>1.723220678082171</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>1.744146541717384</v>
+        <v>1.757598830437495</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>1.397856427813906</v>
+        <v>1.411412474165509</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>1.129826280800252</v>
+        <v>1.1193966451021</v>
       </c>
     </row>
     <row r="18">
@@ -2838,101 +2838,101 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1.915732755627772</v>
+        <v>1.968423176514101</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>2.773294945132655</v>
+        <v>2.824197435873181</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>3.172077032186849</v>
+        <v>3.222377592968371</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>3.125963321760835</v>
+        <v>3.176391282812233</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>1.970258156071395</v>
+        <v>2.02136164161081</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1.82678298620327</v>
+        <v>1.878207036884668</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>2.888433748648815</v>
+        <v>2.9388711269577</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>3.126717722001352</v>
+        <v>3.176648298148947</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>2.801167571268785</v>
+        <v>2.851348961009421</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>3.891077659609458</v>
+        <v>3.939756155868992</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>3.245407227708107</v>
+        <v>3.29452636324757</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>3.279790385053538</v>
+        <v>3.328904515602893</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>3.035902617142149</v>
+        <v>2.996859389161727</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>2.491973155767631</v>
+        <v>2.429643497538031</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; 1.23</t>
+          <t>X &gt; 1.229</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>938</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1.770954003883837</v>
+        <v>1.78347629355946</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>2.611405977273527</v>
+        <v>2.624315786849579</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>3.282635351700392</v>
+        <v>3.295642483117994</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>2.453400211386793</v>
+        <v>2.466379353785257</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.595149572007578</v>
+        <v>1.608260376382518</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.572762085416201</v>
+        <v>1.585804981710567</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>2.554126449167384</v>
+        <v>2.56719270346786</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>2.619992090897604</v>
+        <v>2.633173100192842</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>2.558992204715302</v>
+        <v>2.572190943670066</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>3.414623949324906</v>
+        <v>3.428029076977737</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>2.570211776393243</v>
+        <v>2.583669070103461</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>2.497985125636333</v>
+        <v>2.511437414356443</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>3.143828595714893</v>
+        <v>3.157384642066496</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>2.540671463172416</v>
+        <v>2.530241827474264</v>
       </c>
     </row>
     <row r="20">
@@ -2945,46 +2945,46 @@
         <v>764</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1.433263250470645</v>
+        <v>1.445785540146268</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>2.177710579914766</v>
+        <v>2.190620389490817</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>3.222632449234411</v>
+        <v>3.235639580652013</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>3.614665686553948</v>
+        <v>3.627644828952413</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>2.683574314413725</v>
+        <v>2.696685118788665</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>3.242796356841431</v>
+        <v>3.255839253135797</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>4.074293006061289</v>
+        <v>4.087359260361765</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>3.083549397855712</v>
+        <v>3.09673040715095</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>3.676999773453517</v>
+        <v>3.69019851240828</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>4.004885059629771</v>
+        <v>4.018290187282602</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>3.800131735312192</v>
+        <v>3.81358902902241</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>3.049174578521495</v>
+        <v>3.062626867241605</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>3.414260281712721</v>
+        <v>3.427816328064324</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>2.747751247496865</v>
+        <v>2.737321611798713</v>
       </c>
     </row>
     <row r="21">
@@ -2997,46 +2997,46 @@
         <v>629</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>2.673493317309905</v>
+        <v>2.686015606985528</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>3.446657383200964</v>
+        <v>3.459567192777016</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>4.164666260070199</v>
+        <v>4.177673391487801</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>3.341024321135563</v>
+        <v>3.354003463534028</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>2.484638082216016</v>
+        <v>2.497748886590955</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>2.305132484160609</v>
+        <v>2.318175380454974</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>3.651241374201533</v>
+        <v>3.664307628502009</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>2.389145415801586</v>
+        <v>2.402326425096824</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>2.964075577314041</v>
+        <v>2.977274316268804</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>3.38581048767562</v>
+        <v>3.399215615328451</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>3.816987211052798</v>
+        <v>3.830444504763015</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>2.738492784932411</v>
+        <v>2.751945073652522</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>3.113150733605949</v>
+        <v>3.126706779957551</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>2.567959506263797</v>
+        <v>2.557529870565645</v>
       </c>
     </row>
     <row r="22">
@@ -3046,49 +3046,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>3.345977738184189</v>
+        <v>3.256788887498431</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>3.376739891643282</v>
+        <v>3.467096419206918</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>4.259243447820417</v>
+        <v>4.347370571792496</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>3.65956957312865</v>
+        <v>3.74899826547194</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>2.391221350757213</v>
+        <v>2.482111262467313</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>2.141218032998417</v>
+        <v>2.233037204670708</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>3.516338330324679</v>
+        <v>3.423372382745164</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1.954264420594278</v>
+        <v>2.045556926572267</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>2.075746286236793</v>
+        <v>2.166724132526717</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>2.138029860332949</v>
+        <v>2.227552148583023</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>3.028167046964278</v>
+        <v>3.115747165186207</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>1.967659693360801</v>
+        <v>2.057229142678153</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>2.642295593364807</v>
+        <v>2.729974464228121</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>1.797126414692187</v>
+        <v>1.862813939591277</v>
       </c>
     </row>
     <row r="23">
@@ -3101,46 +3101,46 @@
         <v>466</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>4.588106744167703</v>
+        <v>4.600629033843326</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>4.478679053950223</v>
+        <v>4.491588863526275</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>5.585956270100425</v>
+        <v>5.598963401518027</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>5.072432578673592</v>
+        <v>5.085411721072056</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>3.675642264888964</v>
+        <v>3.688753069263903</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>2.900122829214069</v>
+        <v>2.913165725508435</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>3.673758210654242</v>
+        <v>3.686824464954718</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>2.133613438482186</v>
+        <v>2.146794447777424</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>2.930982651012329</v>
+        <v>2.944181389967092</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>2.080857465984401</v>
+        <v>2.094262593637232</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>3.163657789735495</v>
+        <v>3.177115083445713</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>1.481302749656031</v>
+        <v>1.494755038376141</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>2.134009512101684</v>
+        <v>2.147565558453287</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>1.096177196309299</v>
+        <v>1.085747560611146</v>
       </c>
     </row>
     <row r="24">
@@ -3153,46 +3153,46 @@
         <v>392</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>4.649418822647164</v>
+        <v>4.661941112322786</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>6.099069699478832</v>
+        <v>6.111979509054883</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>6.979711196963869</v>
+        <v>6.992718328381471</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>5.834454125489742</v>
+        <v>5.847433267888206</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>5.296032910417573</v>
+        <v>5.309143714792512</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>3.552658521602616</v>
+        <v>3.565701417896982</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>5.508741130860955</v>
+        <v>5.521807385161431</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>3.76604752799782</v>
+        <v>3.779228537293058</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>4.470353764264502</v>
+        <v>4.483552503219265</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>3.365126538420242</v>
+        <v>3.378531666073073</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>5.201189540633273</v>
+        <v>5.21464683434349</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>2.174348208182785</v>
+        <v>2.187800496902895</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>3.029603801319524</v>
+        <v>3.043159847671127</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>2.258916970330503</v>
+        <v>2.248487334632351</v>
       </c>
     </row>
     <row r="25">
@@ -3205,98 +3205,98 @@
         <v>338</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>4.015437419434996</v>
+        <v>4.027959709110618</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>7.137591617121629</v>
+        <v>7.15050142669768</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>7.630296875022076</v>
+        <v>7.643304006439678</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>7.464692019463904</v>
+        <v>7.477671161862368</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>6.038696839894683</v>
+        <v>6.051807644269623</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>4.560990848616264</v>
+        <v>4.574033744910629</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>6.251405060338065</v>
+        <v>6.264471314638541</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>4.009073732562484</v>
+        <v>4.022254741857722</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>5.131505799042905</v>
+        <v>5.144704537997669</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>4.281380614014978</v>
+        <v>4.294785741667809</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>6.147633206857158</v>
+        <v>6.161090500567376</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>2.927578494380107</v>
+        <v>2.941030783100217</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>4.282471812429286</v>
+        <v>4.296027858780889</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>3.644619180208529</v>
+        <v>3.634189544510377</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 1.649</t>
+          <t>X &gt; 1.648</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>289</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>3.907945762835006</v>
+        <v>3.920468052510628</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>5.410559001081822</v>
+        <v>5.423468810657873</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>6.399773339467934</v>
+        <v>6.412780470885536</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>5.837984949584083</v>
+        <v>5.850964091982547</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>5.299563734511914</v>
+        <v>5.312674538886853</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>4.558943388490547</v>
+        <v>4.571986284784913</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>5.512271954955295</v>
+        <v>5.525338209255771</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>3.314984749945417</v>
+        <v>3.328165759240655</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>4.292047147500142</v>
+        <v>4.305245886454905</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>4.479984246209234</v>
+        <v>4.493389373862065</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>6.005334728120033</v>
+        <v>6.018792021830251</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>1.887468750517371</v>
+        <v>1.900921039237481</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>3.197317945800833</v>
+        <v>3.210873992152436</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>3.101018516831452</v>
+        <v>3.0905888811333</v>
       </c>
     </row>
     <row r="27">
@@ -3309,46 +3309,46 @@
         <v>249</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>4.53467412958922</v>
+        <v>4.547196419264843</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>6.135951922247457</v>
+        <v>6.148861731823509</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>6.544296067056493</v>
+        <v>6.557303198474095</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>6.674549199663993</v>
+        <v>6.687528342062457</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>6.537734410294625</v>
+        <v>6.550845214669565</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>6.433569922307484</v>
+        <v>6.446612818601849</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>7.553655482143633</v>
+        <v>7.566721736444109</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>5.881652806253705</v>
+        <v>5.894833815548942</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>7.828685048585449</v>
+        <v>7.841883787540212</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>7.380166289260337</v>
+        <v>7.393571416913169</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>8.781838667754002</v>
+        <v>8.79529596146422</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>4.398551142368511</v>
+        <v>4.412003431088621</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>5.584722234234853</v>
+        <v>5.598278280586456</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>4.629624289402713</v>
+        <v>4.619194653704561</v>
       </c>
     </row>
     <row r="28">
@@ -3361,46 +3361,46 @@
         <v>212</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>4.582033377903237</v>
+        <v>4.594555667578859</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>5.800648444184262</v>
+        <v>5.813558253760313</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>7.292572190417857</v>
+        <v>7.305579321835459</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>6.479429096610268</v>
+        <v>6.492408239008732</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>7.827800334368284</v>
+        <v>7.840911138743223</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>6.710147932461297</v>
+        <v>6.723190828755662</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>7.09711232839657</v>
+        <v>7.110178582697046</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>5.68653270319998</v>
+        <v>5.699713712495218</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>8.45572149626296</v>
+        <v>8.468920235217723</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>9.020690650857674</v>
+        <v>9.034095778510505</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>10.70272977937027</v>
+        <v>10.71618707308049</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>4.133339351810051</v>
+        <v>4.146791640530161</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>5.12817908048779</v>
+        <v>5.141735126839393</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>3.491107959933892</v>
+        <v>3.48067832423574</v>
       </c>
     </row>
     <row r="29">
@@ -3413,46 +3413,46 @@
         <v>186</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>3.420540174413674</v>
+        <v>3.433062464089296</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>6.647676238868783</v>
+        <v>6.660586048444834</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>7.865710758078642</v>
+        <v>7.878717889496244</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>7.45832948208399</v>
+        <v>7.471308624482454</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>7.995177084216124</v>
+        <v>8.008287888591063</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>6.679715796125329</v>
+        <v>6.692758692419694</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>7.132616487455202</v>
+        <v>7.145682741755678</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>5.590164271469405</v>
+        <v>5.603345280764643</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>7.679702019695704</v>
+        <v>7.692900758650467</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>7.367211243269921</v>
+        <v>7.380616370922752</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>8.77536114475879</v>
+        <v>8.788818438469008</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>2.895765807480572</v>
+        <v>2.909218096200682</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>4.088414422342126</v>
+        <v>4.101970468693729</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>2.187598120209813</v>
+        <v>2.177168484511661</v>
       </c>
     </row>
     <row r="30">
@@ -3465,46 +3465,46 @@
         <v>156</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>1.352715525943871</v>
+        <v>1.365237815619494</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>8.715500887338585</v>
+        <v>8.728410696914636</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>7.67960653971636</v>
+        <v>7.692613671133962</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>7.80985967232386</v>
+        <v>7.822838814722324</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>9.83554102135426</v>
+        <v>9.848651825729199</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>7.568880394967351</v>
+        <v>7.581923291261717</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>8.125172318720708</v>
+        <v>8.138238573021184</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>5.73491199686228</v>
+        <v>5.748093006157518</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>8.238014674782548</v>
+        <v>8.251213413737311</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>8.028915130780263</v>
+        <v>8.042320258433094</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>9.747238729539603</v>
+        <v>9.760696023249821</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>4.653416758679903</v>
+        <v>4.666869047400013</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>6.156239070811928</v>
+        <v>6.169795117163531</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>3.841857838985653</v>
+        <v>3.831428203287501</v>
       </c>
     </row>
     <row r="31">
@@ -3517,150 +3517,150 @@
         <v>132</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>2.052016225244564</v>
+        <v>2.064538514920187</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>10.28892746076516</v>
+        <v>10.30183727034121</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>9.136482996592811</v>
+        <v>9.149490128010413</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>9.266736129200311</v>
+        <v>9.279715271598775</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>10.24346642927966</v>
+        <v>10.2565772336546</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>9.025756851843802</v>
+        <v>9.038799748138167</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>9.698598892147281</v>
+        <v>9.711665146447757</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>6.958688220638514</v>
+        <v>6.971869229933752</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>8.412839849607721</v>
+        <v>8.426038588562484</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>10.59301769488282</v>
+        <v>10.60642282253565</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>10.38826437056524</v>
+        <v>10.40172166427546</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>5.119617224880379</v>
+        <v>5.133069513600489</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>6.972089886662744</v>
+        <v>6.985645933014347</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>4.949083946211765</v>
+        <v>4.938654310513613</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 2.008</t>
+          <t>X &gt; 2.007</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>117</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>1.352715525943871</v>
+        <v>1.365237815619494</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>9.99755216938987</v>
+        <v>10.01046197896592</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>10.45738431749413</v>
+        <v>10.47039144891173</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>9.73293659540078</v>
+        <v>9.745915737799244</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>9.19451538032861</v>
+        <v>9.20762618470355</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>9.491957318044271</v>
+        <v>9.505000214338637</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>8.552522746071133</v>
+        <v>8.56558900037161</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>6.37593763788793</v>
+        <v>6.389118647183167</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>8.87904031580819</v>
+        <v>8.892239054762953</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>11.44771854958368</v>
+        <v>11.46112367723651</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>12.09766607996696</v>
+        <v>12.11112337367717</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>4.439741545004694</v>
+        <v>4.453193833724804</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>7.438290352863213</v>
+        <v>7.451846399214816</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>4.269208266336079</v>
+        <v>4.258778630637927</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 2.068</t>
+          <t>X &gt; 2.067</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>108</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>2.136191309419651</v>
+        <v>2.148713599095274</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>12.56165473349242</v>
+        <v>12.57456454306848</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>13.09271195282177</v>
+        <v>13.10571908423938</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>10.44518730765149</v>
+        <v>10.45816645004995</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>9.906766092579318</v>
+        <v>9.919876896954257</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>10.20420803029498</v>
+        <v>10.21725092658934</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>10.1194743130227</v>
+        <v>10.13254056732318</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>7.800439062389351</v>
+        <v>7.813620071684589</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>9.591291028058897</v>
+        <v>9.604489767013661</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>12.44486954673468</v>
+        <v>12.45827467438751</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>12.2401162224171</v>
+        <v>12.25357351612732</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>3.941166046429196</v>
+        <v>3.954618335149306</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>8.15054106511392</v>
+        <v>8.164097111465523</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>3.770632767760581</v>
+        <v>3.760203132062429</v>
       </c>
     </row>
     <row r="34">
@@ -3673,46 +3673,46 @@
         <v>93</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>2.345271357209377</v>
+        <v>2.357793646885</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>12.56165473349242</v>
+        <v>12.57456454306848</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>13.24205484410014</v>
+        <v>13.25506197551774</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>12.29703915950333</v>
+        <v>12.3100183019018</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>8.532811492818269</v>
+        <v>8.545922297193208</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>8.830253430533929</v>
+        <v>8.843296326828295</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>8.74551971326165</v>
+        <v>8.758585967562126</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>5.052529862867253</v>
+        <v>5.065710872162491</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>9.292605245502152</v>
+        <v>9.305803984456915</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>11.66828651208712</v>
+        <v>11.68169163973995</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>12.53880200497386</v>
+        <v>12.55225929868408</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>2.895765807480572</v>
+        <v>2.909218096200682</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>6.776586465352871</v>
+        <v>6.790142511704474</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>2.725232528811958</v>
+        <v>2.714802893113806</v>
       </c>
     </row>
     <row r="35">
@@ -3725,46 +3725,46 @@
         <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>1.077990251218594</v>
+        <v>1.090512540894217</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>12.56165473349242</v>
+        <v>12.57456454306848</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>10.97630983641966</v>
+        <v>10.98931696783726</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>12.29703915950333</v>
+        <v>12.3100183019018</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>8.187189373002603</v>
+        <v>8.200300177377542</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>7.294155120242074</v>
+        <v>7.307198016536439</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>9.590373783922182</v>
+        <v>9.603440038222658</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>4.361285623235915</v>
+        <v>4.374466632531153</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>9.06219049895838</v>
+        <v>9.075389237913143</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>10.59301769488282</v>
+        <v>10.60642282253565</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>11.57874056104144</v>
+        <v>11.59219785475166</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>2.089314194577348</v>
+        <v>2.102766483297458</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>5.240488155061016</v>
+        <v>5.254044201412619</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>0.7283047254325368</v>
+        <v>0.7178750897343846</v>
       </c>
     </row>
   </sheetData>
@@ -3815,7 +3815,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that Volume Ratio-30 is below threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that Volume Ratio-30 is below threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -3904,53 +3904,53 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; 0.4514</t>
+          <t>X &lt; 0.4515</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-6.064866891638545</v>
+        <v>-6.052344601962922</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-5.295488123650422</v>
+        <v>-5.282578314074371</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-5.690356830247012</v>
+        <v>-5.67734969882941</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-4.369627507163322</v>
+        <v>-4.356648364764858</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-1.336620150806922</v>
+        <v>-1.323509346431983</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.1512979773849352</v>
+        <v>0.1643408736793006</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-1.123911930363541</v>
+        <v>-1.110845676063065</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.7898570518073456</v>
+        <v>0.8030380611025834</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>6.681238118005993</v>
+        <v>6.694436856960756</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>5.831112932978066</v>
+        <v>5.844518060630897</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>11.57874056104144</v>
+        <v>11.59219785475166</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>9.232171337434494</v>
+        <v>9.245623626154604</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>8.811916726489592</v>
+        <v>8.825472772841195</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>4.299733296861106</v>
+        <v>4.289303661162954</v>
       </c>
     </row>
     <row r="7">
@@ -3963,98 +3963,98 @@
         <v>165</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-6.385653889072245</v>
+        <v>-6.373131599396622</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-2.0092035499407</v>
+        <v>-1.996293740364649</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>2.126625384325571</v>
+        <v>1.800551641347376</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>1.052059239824629</v>
+        <v>1.065038382223094</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>4.730505494631977</v>
+        <v>4.743616299006916</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>3.220718516684983</v>
+        <v>3.233761412979348</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>1.931165522304283</v>
+        <v>1.944231776604759</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>2.066391762076996</v>
+        <v>2.079572771372234</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>5.017440068665778</v>
+        <v>5.030638807620541</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>5.974543799300505</v>
+        <v>5.987948926953337</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>7.357961340262214</v>
+        <v>6.988067045801571</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>5.574162679425825</v>
+        <v>5.587614968145935</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>5.153908068480924</v>
+        <v>5.167464114832526</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>2.979386976514796</v>
+        <v>2.968957340816644</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; 0.5712</t>
+          <t>X &lt; 0.5711</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>281</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-1.789212968097303</v>
+        <v>-1.77669067842168</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.4724528555581671</v>
+        <v>0.4853626651342182</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>2.037221833727415</v>
+        <v>1.851154660660868</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.8235282163831741</v>
+        <v>-0.999757905400898</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.6527295732993252</v>
+        <v>-0.639618768924386</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.7085421516503843</v>
+        <v>0.7215850479447496</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>1.68763822161214</v>
+        <v>1.700704475912616</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>1.575064751908663</v>
+        <v>1.5882457612039</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>1.86867479480437</v>
+        <v>1.881873533759133</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>3.855429042400559</v>
+        <v>3.86883417005339</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>5.999177775072958</v>
+        <v>5.791792586261273</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>3.54245772957141</v>
+        <v>3.55591001829152</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>1.698715574142525</v>
+        <v>1.712271620494128</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.5249493619348371</v>
+        <v>0.514519726236685</v>
       </c>
     </row>
     <row r="9">
@@ -4067,98 +4067,98 @@
         <v>439</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-1.588460944644368</v>
+        <v>-1.575938654968745</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>1.777341008002239</v>
+        <v>1.79025081757829</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>1.962704394242778</v>
+        <v>1.847968120606055</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.278718416254236</v>
+        <v>-0.3883943965108898</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.3625941767809522</v>
+        <v>-0.3494833724060129</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>2.207575033661989</v>
+        <v>2.220617929956354</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>1.44102313457153</v>
+        <v>1.454089388872006</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>1.65565791760821</v>
+        <v>1.668838926903447</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>2.276476213244081</v>
+        <v>2.289674952198844</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>3.017260119125254</v>
+        <v>3.030665246778085</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>4.769433694786962</v>
+        <v>4.644145906699713</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>3.209283822519637</v>
+        <v>3.222736111239747</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>2.105657913169267</v>
+        <v>2.11921395952087</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>1.216427081436443</v>
+        <v>1.205997445738291</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; 0.6909</t>
+          <t>X &lt; 0.6908</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>644</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.4133150536460235</v>
+        <v>-0.4007927639704008</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.7486090221416433</v>
+        <v>0.7615188317176944</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>1.518637878747704</v>
+        <v>1.445329881477285</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.2738006138093851</v>
+        <v>-0.3443026857525169</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.2640858739382779</v>
+        <v>-0.3354325082778686</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1.426544918266551</v>
+        <v>1.439587814560916</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>1.496609962604182</v>
+        <v>1.509676216904658</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.7198290406028605</v>
+        <v>0.7330100498980983</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>1.897219247299823</v>
+        <v>1.910417986254586</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>3.151157229766547</v>
+        <v>3.072883090853516</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>4.125324411973118</v>
+        <v>4.045132516988645</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>3.228030550685013</v>
+        <v>3.241482839405123</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>2.031378424212157</v>
+        <v>2.04493447056376</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.5730252223269474</v>
+        <v>0.5625955866287953</v>
       </c>
     </row>
     <row r="11">
@@ -4171,98 +4171,98 @@
         <v>894</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.1601049868766466</v>
+        <v>-0.1475826972010239</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>1.450543622381325</v>
+        <v>1.463453431957376</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>1.228706679472786</v>
+        <v>1.179793158313444</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.2493602465842528</v>
+        <v>-0.2965816239417265</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.1700331146546645</v>
+        <v>-0.2178777842302679</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>1.130753304666342</v>
+        <v>1.143796200960708</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>1.603433188285933</v>
+        <v>1.616499442586409</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.9758689565692507</v>
+        <v>0.9264653584429183</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>2.03094049895838</v>
+        <v>2.044139237913143</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>2.473837061735722</v>
+        <v>2.421899013011853</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>3.229427681527213</v>
+        <v>3.176395779731706</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>2.592669899275336</v>
+        <v>2.606122187995446</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>2.060558465064211</v>
+        <v>2.074114511415814</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>1.527282034476961</v>
+        <v>1.516852398778809</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; 0.8106</t>
+          <t>X &lt; 0.8105</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-1.672420257812604</v>
+        <v>-1.659897968136981</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.5747910224907926</v>
+        <v>0.5877008320668438</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.6356986535734706</v>
+        <v>0.6034384785104976</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.257785401900172</v>
+        <v>-0.2892695644361751</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.4828977798221246</v>
+        <v>0.4504568189815501</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1.438775931529548</v>
+        <v>1.451818827823914</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>1.51865126775521</v>
+        <v>1.531717522055686</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.9330279939898105</v>
+        <v>0.9000398247710066</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>1.531006691003554</v>
+        <v>1.544205429958318</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>1.222311456905359</v>
+        <v>1.188520571025499</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>2.054931037231917</v>
+        <v>2.020298196289758</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>1.476872686182084</v>
+        <v>1.442700476696793</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>1.1391944583916</v>
+        <v>1.152750504743203</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.6102409710051475</v>
+        <v>0.6352987065799667</v>
       </c>
     </row>
     <row r="13">
@@ -4272,153 +4272,153 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1538</v>
+        <v>1539</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-1.007650206514889</v>
+        <v>-0.9951279168392659</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.1295756047967274</v>
+        <v>-0.1515336481459784</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.2954821921640942</v>
+        <v>-0.3175134566402278</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.6479446592668907</v>
+        <v>-0.6697143414789579</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.01423107051061834</v>
+        <v>-0.008206526274790349</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.5059735263609966</v>
+        <v>0.519016422655362</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.1621724515757634</v>
+        <v>0.1752387058762395</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.01022318767665809</v>
+        <v>-0.03276258039754509</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.7712915081241931</v>
+        <v>0.7844902470789563</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.04252056711457897</v>
+        <v>-0.06542854925090325</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.6975873210303121</v>
+        <v>0.6740952051314935</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.3144224196855774</v>
+        <v>0.2911722803989036</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.2558042230086599</v>
+        <v>0.2323991797675902</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.2824566853062223</v>
+        <v>0.3001641457076545</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; 0.9303</t>
+          <t>X &lt; 0.9302</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>1879</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-1.435237262008918</v>
+        <v>-1.422714972333296</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.5316927166575525</v>
+        <v>-0.5187829070815013</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-1.163016232991161</v>
+        <v>-1.20297520326848</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-1.375456865933856</v>
+        <v>-1.415471894176619</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.02302232760543887</v>
+        <v>-0.01688913737274333</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.5087566107056318</v>
+        <v>0.4687491091220153</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.2648716997994001</v>
+        <v>0.2540314849924457</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.06698249929972633</v>
+        <v>-0.1068800462677544</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.03125328330778387</v>
+        <v>0.02068929101987749</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.0460334646144247</v>
+        <v>-0.08573508151815901</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.3103330917838036</v>
+        <v>0.270655422688499</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.1036682615630085</v>
+        <v>-0.1433791839008478</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.4633858247671938</v>
+        <v>0.4237503817570882</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.1080063822995285</v>
+        <v>-0.1184360179976807</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; 0.9902</t>
+          <t>X &lt; 0.9901</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2197</v>
+        <v>2198</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-1.000225650526723</v>
+        <v>-1.0109929188202</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.9135225714721074</v>
+        <v>-0.9246813091185402</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-1.148431364408502</v>
+        <v>-1.159576088706316</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-1.356487498101245</v>
+        <v>-1.367517929982256</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.1483025753633243</v>
+        <v>-0.1600036179058648</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.128622240423482</v>
+        <v>0.1168513429622067</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.3396236233892083</v>
+        <v>-0.3512084878544499</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.7821335238146432</v>
+        <v>-0.7936260128754711</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.7730242408885175</v>
+        <v>-0.7845420246508965</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-1.053203719625728</v>
+        <v>-1.06478517019822</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.5511295688286921</v>
+        <v>-0.5629913449627608</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.8552060418937799</v>
+        <v>-0.866930486399518</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.4313347142140813</v>
+        <v>-0.4433507183561076</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.5201509608929626</v>
+        <v>-0.5105143552155624</v>
       </c>
     </row>
     <row r="16">
@@ -4428,49 +4428,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2499</v>
+        <v>2500</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.7418459635220742</v>
+        <v>-0.7499172243266372</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.7796435540424085</v>
+        <v>-0.7879619962096456</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-1.033745181603493</v>
+        <v>-1.042030816198704</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-1.400317024899472</v>
+        <v>-1.408441193450116</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.3227217684874901</v>
+        <v>-0.3313667739785231</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.2358232114913363</v>
+        <v>0.2269975152833084</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.3058752184720817</v>
+        <v>-0.3145040041729317</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.6315857768211188</v>
+        <v>-0.6401649184132552</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.3912554161488799</v>
+        <v>-0.3999458062841796</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.9398095790551153</v>
+        <v>-0.9484227578690252</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.4830385870686413</v>
+        <v>-0.4918726891670744</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.7062342527104022</v>
+        <v>-0.7149793200598609</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.4642737497008866</v>
+        <v>-0.473188714944655</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.2320794282289285</v>
+        <v>-0.2249820531227513</v>
       </c>
     </row>
     <row r="17">
@@ -4480,49 +4480,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2797</v>
+        <v>2798</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.4293813807081932</v>
+        <v>-0.4353806338783599</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-1.02562425072496</v>
+        <v>-1.031603902957606</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-1.294752434642618</v>
+        <v>-1.300686253102235</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-1.216795301962037</v>
+        <v>-1.222745230861719</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.6314984727700619</v>
+        <v>-0.6377238102723837</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.2077547346089545</v>
+        <v>-0.2140998825233993</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.6653832977978169</v>
+        <v>-0.671579060325854</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.7565303222646591</v>
+        <v>-0.7627523063996264</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.4412254284404256</v>
+        <v>-0.4475708558639369</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.950478675461099</v>
+        <v>-0.9567463423465696</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.5998308675299882</v>
+        <v>-0.6062516785782748</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.5812824470803903</v>
+        <v>-0.5877097071787389</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.4098062729317675</v>
+        <v>-0.4163482857001313</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.2829828786330424</v>
+        <v>-0.2777340188125308</v>
       </c>
     </row>
     <row r="18">
@@ -4535,98 +4535,98 @@
         <v>3015</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.6770578710686195</v>
+        <v>-0.6975606804682997</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.9500730497913494</v>
+        <v>-0.9701992494653737</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-1.162141049552709</v>
+        <v>-1.182180844770933</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-1.11342916005588</v>
+        <v>-1.133507868897084</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.6752444894312575</v>
+        <v>-0.6952024681250961</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.5583408235539054</v>
+        <v>-0.5783776493898714</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.8899136321693462</v>
+        <v>-0.9099380463003683</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.9751687201697692</v>
+        <v>-0.9950893328540147</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.7864376940406785</v>
+        <v>-0.8063515378673713</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.221048773042533</v>
+        <v>-1.240767196234351</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.01001263407359</v>
+        <v>-1.029689866539641</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.9904559965617565</v>
+        <v>-1.010149216625209</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.8950429804701159</v>
+        <v>-0.881486934118513</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.6931593825987292</v>
+        <v>-0.6704215224428225</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; 1.23</t>
+          <t>X &lt; 1.229</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3211</v>
+        <v>3212</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.4773092879519112</v>
+        <v>-0.4809160305343525</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.6765291531556201</v>
+        <v>-0.6801914536229958</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.9306689700004895</v>
+        <v>-0.9342827543972803</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.6595995655302929</v>
+        <v>-0.6632902021329485</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.4049431321733863</v>
+        <v>-0.4087535030825364</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.3390938923172868</v>
+        <v>-0.3429055031323003</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.5623386372799928</v>
+        <v>-0.5660890968237311</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.5775068038996949</v>
+        <v>-0.58128819892287</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.4971556275519404</v>
+        <v>-0.5009685044377648</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.7703830308818169</v>
+        <v>-0.7741741923897081</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.5534489669166049</v>
+        <v>-0.5573244736198149</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.5017222199884799</v>
+        <v>-0.5056135208510639</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.6866896899250463</v>
+        <v>-0.6905558608345004</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.5129641271723457</v>
+        <v>-0.5096644939695736</v>
       </c>
     </row>
     <row r="20">
@@ -4636,49 +4636,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3385</v>
+        <v>3386</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.2862576256837883</v>
+        <v>-0.2890949066743929</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.4105756658795556</v>
+        <v>-0.4134676327211935</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.701294067332654</v>
+        <v>-0.704124023513657</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.7613800844829086</v>
+        <v>-0.7641866450946537</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.5474123050286579</v>
+        <v>-0.5503134701433225</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.6170907220382489</v>
+        <v>-0.619956345503013</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.744868803678898</v>
+        <v>-0.7477030715411459</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.5178763039944343</v>
+        <v>-0.5208051554293149</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.5922553501777372</v>
+        <v>-0.5951672772319938</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.6885796297950506</v>
+        <v>-0.6915122807091834</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.6703739608003545</v>
+        <v>-0.6733250555042147</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.4719494605747059</v>
+        <v>-0.4749588217005751</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.5508655984900273</v>
+        <v>-0.5538768412294175</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.4027355784290378</v>
+        <v>-0.4001740200453767</v>
       </c>
     </row>
     <row r="21">
@@ -4688,49 +4688,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3520</v>
+        <v>3521</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.4413579352679946</v>
+        <v>-0.4435645874104139</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.5376280147144357</v>
+        <v>-0.5398802158710296</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.7190819991590942</v>
+        <v>-0.72130159442343</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.5452649009310306</v>
+        <v>-0.5475291350848792</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.3883547579396591</v>
+        <v>-0.3906886260758498</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.3022167618440932</v>
+        <v>-0.3045630381262825</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.4849634107799119</v>
+        <v>-0.4872629096231549</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.2561143713620382</v>
+        <v>-0.2585008158601738</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.3015379711530741</v>
+        <v>-0.3039155185895765</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.3982800728053988</v>
+        <v>-0.4006693760459044</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.502075302062245</v>
+        <v>-0.5044455699280945</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.2814978440370766</v>
+        <v>-0.2839304605950588</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.3450462575111715</v>
+        <v>-0.3474809060750061</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.2497796901518754</v>
+        <v>-0.2477596731170806</v>
       </c>
     </row>
     <row r="22">
@@ -4743,46 +4743,46 @@
         <v>3601</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.4735157966903287</v>
+        <v>-0.460993507014706</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.4376994504728771</v>
+        <v>-0.4524674709549501</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.6239116475227675</v>
+        <v>-0.638590008906931</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.5064317165236076</v>
+        <v>-0.5211457339146719</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.3097107720969845</v>
+        <v>-0.3243007987469753</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.2188085024472315</v>
+        <v>-0.2334741126643678</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.3716154463597405</v>
+        <v>-0.3585491920592645</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.1306414497834822</v>
+        <v>-0.1451843107405324</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.09318546174205267</v>
+        <v>-0.1077182813008761</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.1235796236562408</v>
+        <v>-0.1379137470436262</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.2850615635819906</v>
+        <v>-0.2993512177075104</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.09636440658834999</v>
+        <v>-0.1106667667719279</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.1956452100007198</v>
+        <v>-0.2098515178967517</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.06909282286753182</v>
+        <v>-0.07952245856568396</v>
       </c>
     </row>
     <row r="23">
@@ -4792,49 +4792,49 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3683</v>
+        <v>3684</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.5453863721580348</v>
+        <v>-0.5469154895551753</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.4920214054340448</v>
+        <v>-0.4936172751133299</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.6828800983523067</v>
+        <v>-0.6844377844019363</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.5922107728010175</v>
+        <v>-0.5937896749976659</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.4118407049007118</v>
+        <v>-0.4134865233303628</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.2621917208514475</v>
+        <v>-0.2638694136859243</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.3050965993530852</v>
+        <v>-0.3067662550776475</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.106953285230702</v>
+        <v>-0.1086924847743092</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.1530248713546101</v>
+        <v>-0.1547544324582404</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.06605472171603566</v>
+        <v>-0.06783603502037749</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.228483685141029</v>
+        <v>-0.2302284306526587</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.011069056630717</v>
+        <v>0.009259520012953715</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.0681825444891615</v>
+        <v>-0.06998500321360268</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.06114674087026373</v>
+        <v>0.06253151908137511</v>
       </c>
     </row>
     <row r="24">
@@ -4844,49 +4844,49 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3757</v>
+        <v>3758</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.4509980019075925</v>
+        <v>-0.4522764123959249</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.5629583380561627</v>
+        <v>-0.5642506647122332</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.7047638669470402</v>
+        <v>-0.7060297832271942</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.5602301087030099</v>
+        <v>-0.5615315919410762</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.5001889240411259</v>
+        <v>-0.5015214060474449</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.2679773024481165</v>
+        <v>-0.2693642068659301</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.4179759959472591</v>
+        <v>-0.4193260403203212</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.232946435784875</v>
+        <v>-0.2343588317672101</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.2527635528377843</v>
+        <v>-0.2541730414232575</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.1576691791754925</v>
+        <v>-0.1591274166987873</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.3741469769524883</v>
+        <v>-0.3755538830080525</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.03226069236066564</v>
+        <v>-0.03375833939757911</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.1182386246343583</v>
+        <v>-0.1197254181670644</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.0397853160138979</v>
+        <v>-0.03860632135053521</v>
       </c>
     </row>
     <row r="25">
@@ -4896,101 +4896,101 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3811</v>
+        <v>3812</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.3229362281597687</v>
+        <v>-0.3240532854363067</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.5606750249869492</v>
+        <v>-0.5617673955647149</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.6537267936169755</v>
+        <v>-0.6548044526378192</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.614066135794566</v>
+        <v>-0.6151517661254005</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.4839649526019798</v>
+        <v>-0.4850975619327897</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.3031964676829659</v>
+        <v>-0.3043701709479762</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.3998978616663891</v>
+        <v>-0.4010487958027156</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.1978919906967391</v>
+        <v>-0.1991071657676287</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.2444881473429135</v>
+        <v>-0.2456931379242775</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.1889831788611644</v>
+        <v>-0.1902228797704169</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.3790839951050913</v>
+        <v>-0.3802792094685259</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.06777995700932848</v>
+        <v>-0.06905662455081796</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.184735449595955</v>
+        <v>-0.1859917657673265</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.1301126378391899</v>
+        <v>-0.1290743931017744</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 1.649</t>
+          <t>X &lt; 1.648</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3860</v>
+        <v>3861</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.2600275275427961</v>
+        <v>-0.2609883072509191</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.3343507761494422</v>
+        <v>-0.3353244318863275</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.4569976637956188</v>
+        <v>-0.4579478885185111</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.3902993417886478</v>
+        <v>-0.3912647429617024</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.3461464218994834</v>
+        <v>-0.3471343002894969</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.2414237441889142</v>
+        <v>-0.2424333635420837</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.2603779985596333</v>
+        <v>-0.2613848989911247</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.09268427305162419</v>
+        <v>-0.09374423599003023</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.1135625965877338</v>
+        <v>-0.1146188915673108</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.1471479365871531</v>
+        <v>-0.1482127962655468</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.2856505487547949</v>
+        <v>-0.2866841328259824</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.04805750546979937</v>
+        <v>0.04693768012202781</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.04681713224427142</v>
+        <v>-0.04792122484074213</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.04149542260595496</v>
+        <v>-0.04062566876637419</v>
       </c>
     </row>
     <row r="27">
@@ -5000,49 +5000,49 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3900</v>
+        <v>3901</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.2573023631437863</v>
+        <v>-0.2581260458639392</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.3217808493296488</v>
+        <v>-0.3226157959723253</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.3960708724478934</v>
+        <v>-0.3968939582509705</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.3798576861914569</v>
+        <v>-0.3806831384800162</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.3672454477407356</v>
+        <v>-0.3680836979117004</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.3117326801186024</v>
+        <v>-0.312580516519148</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.3313783825190058</v>
+        <v>-0.3322230704189693</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.2214076691347984</v>
+        <v>-0.2222888856474583</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.2939463219671765</v>
+        <v>-0.2948104548672035</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.2847145455543298</v>
+        <v>-0.2855959568070645</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.3983100593604547</v>
+        <v>-0.3991663138666084</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.09332718591128497</v>
+        <v>-0.09426144393800229</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.1659399891266773</v>
+        <v>-0.1668632697255035</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.1068601097322954</v>
+        <v>-0.1060894614795913</v>
       </c>
     </row>
     <row r="28">
@@ -5052,49 +5052,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3937</v>
+        <v>3938</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.2149573075517495</v>
+        <v>-0.21566672656067</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.2432747845290066</v>
+        <v>-0.24400085777539</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.3712078940768038</v>
+        <v>-0.3719076942230615</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.3032479784073061</v>
+        <v>-0.3039634610161173</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.3718094926358972</v>
+        <v>-0.3725158251318987</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.2633317528341479</v>
+        <v>-0.2640616074347975</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.2328658567616841</v>
+        <v>-0.2336050459707195</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.1536474105913612</v>
+        <v>-0.1544138851931791</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.2514284037016239</v>
+        <v>-0.252171357717458</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.301002435371764</v>
+        <v>-0.3017456198793553</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.4154581336648704</v>
+        <v>-0.4161756545099564</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.03685996129977553</v>
+        <v>-0.03767344902064451</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.08733113923872082</v>
+        <v>-0.0881383684927215</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.001039590398946189</v>
+        <v>-0.0004010475361582166</v>
       </c>
     </row>
     <row r="29">
@@ -5104,49 +5104,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3963</v>
+        <v>3964</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.1292532095459933</v>
+        <v>-0.1298976749899765</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.2433767130484483</v>
+        <v>-0.2440135924110578</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.3478927182811375</v>
+        <v>-0.348508728479004</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.3046891734104875</v>
+        <v>-0.3053146959173461</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.3259742005839357</v>
+        <v>-0.326601648039258</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.2162476810194534</v>
+        <v>-0.2168992356574861</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.1865243808853094</v>
+        <v>-0.1871848493551482</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.1108736108280866</v>
+        <v>-0.1115595159635063</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.1579995932075278</v>
+        <v>-0.1586747580556249</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.1623810111082662</v>
+        <v>-0.1630664247761686</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.2521794014972798</v>
+        <v>-0.252845178846961</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>0.04854076036129129</v>
+        <v>0.04779926191570638</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.004334294605023103</v>
+        <v>-0.005068270814604148</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>0.08305040871721303</v>
+        <v>0.08359514163002046</v>
       </c>
     </row>
     <row r="30">
@@ -5156,49 +5156,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3993</v>
+        <v>3994</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.02214525980058824</v>
+        <v>-0.02271787730250452</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.2723028195662422</v>
+        <v>-0.2728310302382226</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.2791014189915941</v>
+        <v>-0.2796325595392375</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.2602095706157357</v>
+        <v>-0.2607442688607691</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.3353350790570886</v>
+        <v>-0.3358572283776695</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.1992096338075058</v>
+        <v>-0.199762788775196</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.1703405017921114</v>
+        <v>-0.1709020905308734</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.07375170752534643</v>
+        <v>-0.07434289127837701</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.1209725111180902</v>
+        <v>-0.1215528547528848</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.1316925044333246</v>
+        <v>-0.1322798621400167</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.2223462400453613</v>
+        <v>-0.2229134787484668</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.001287494535624489</v>
+        <v>0.000664381195349506</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.05435887739242418</v>
+        <v>-0.05497302249821701</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.03423295698060258</v>
+        <v>0.03470748117869249</v>
       </c>
     </row>
     <row r="31">
@@ -5208,153 +5208,153 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4017</v>
+        <v>4018</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.03686263782783783</v>
+        <v>-0.03735363906821476</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.270313496837673</v>
+        <v>-0.2707621732259753</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.2794238373874975</v>
+        <v>-0.2798742529548619</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.2598683812631535</v>
+        <v>-0.2603226448045746</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.2880785284948075</v>
+        <v>-0.2885311634528094</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.2006688963210763</v>
+        <v>-0.2011406393432011</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.1724776787304734</v>
+        <v>-0.1729574773053031</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.07925270991987077</v>
+        <v>-0.07976038630818749</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.07683059928699265</v>
+        <v>-0.07733971347353474</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.167158049127778</v>
+        <v>-0.1676530932607889</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.183874932917341</v>
+        <v>-0.1843680314884395</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0.01375642730521776</v>
+        <v>0.01321424449148623</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.04406469046743666</v>
+        <v>-0.04459677774590176</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>0.0205981924832912</v>
+        <v>0.02101097823613429</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 2.008</t>
+          <t>X &lt; 2.007</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4032</v>
+        <v>4033</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.008889494499221939</v>
+        <v>-0.009339164493816554</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.2227171755085493</v>
+        <v>-0.2231280815709837</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.2827151685860656</v>
+        <v>-0.2831148535559933</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.2380094962776269</v>
+        <v>-0.2384193269216652</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.2186154136485072</v>
+        <v>-0.2190348995527813</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.1799137152128978</v>
+        <v>-0.1803404286857457</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.1026195312548523</v>
+        <v>-0.1030663266995475</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.03622375198519734</v>
+        <v>-0.03669124483123198</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.05879750486341351</v>
+        <v>-0.05926016419540048</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.1519443137065295</v>
+        <v>-0.1523914785129676</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.1941395947383455</v>
+        <v>-0.1945783026885195</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.05246078191828474</v>
+        <v>0.05196103100501404</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.03149418114150393</v>
+        <v>-0.03197699933341625</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.05866186828968978</v>
+        <v>0.05902488959979024</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 2.068</t>
+          <t>X &lt; 2.067</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4041</v>
+        <v>4042</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.02673876421589938</v>
+        <v>-0.02715524138515946</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.2683477338157374</v>
+        <v>-0.2687178118073561</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.3291007779741761</v>
+        <v>-0.3294592473120161</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.234845971739972</v>
+        <v>-0.2352268445279364</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.2166906975441307</v>
+        <v>-0.2170805986801057</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.1774134034380879</v>
+        <v>-0.1778108018057125</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.1251823990253129</v>
+        <v>-0.125593585599816</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.05997880544141765</v>
+        <v>-0.06041008495426325</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.05792813673119923</v>
+        <v>-0.05836062971367539</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.1527589841447821</v>
+        <v>-0.1531751342941376</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.1705882506019165</v>
+        <v>-0.1710018627125862</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.07554554093731269</v>
+        <v>0.07507113215996952</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.03389275019569737</v>
+        <v>-0.03434372363125959</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>0.08136443483969202</v>
+        <v>0.08169780833196683</v>
       </c>
     </row>
     <row r="34">
@@ -5364,49 +5364,49 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4056</v>
+        <v>4057</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.02354399728050538</v>
+        <v>-0.0239135735318996</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.2210394651309713</v>
+        <v>-0.2213722145296089</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.283013169891305</v>
+        <v>-0.2833336853443669</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.2378026178372039</v>
+        <v>-0.2381334889350128</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.147901120759478</v>
+        <v>-0.1482581342894775</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.1076540286143199</v>
+        <v>-0.1080189927765147</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.05591150843744686</v>
+        <v>-0.05628999552313019</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>0.03196157456179094</v>
+        <v>0.03155792092935883</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.01544695838852306</v>
+        <v>-0.01583957266574743</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.08842729690698548</v>
+        <v>-0.08880823713766262</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.1315681004867386</v>
+        <v>-0.1319400762828238</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.1137925911602338</v>
+        <v>0.1133602255985124</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.02786329737823934</v>
+        <v>0.02744888117510413</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>0.1189781545675075</v>
+        <v>0.119262462529214</v>
       </c>
     </row>
     <row r="35">
@@ -5416,49 +5416,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4065</v>
+        <v>4066</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.007787771011209088</v>
+        <v>0.007438958433539256</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.1928215971428386</v>
+        <v>-0.1931320402239862</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.2064557133723994</v>
+        <v>-0.2067655858611914</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.2101183047093329</v>
+        <v>-0.210426578700087</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.121598059496165</v>
+        <v>-0.1219317828912239</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.0562242654920837</v>
+        <v>-0.05657223383175136</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.05388667075085607</v>
+        <v>-0.05423594648500085</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.05732380269340354</v>
+        <v>0.05694394565679772</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.009891446659317182</v>
+        <v>0.009522655465865171</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.0402255262198139</v>
+        <v>-0.04058782447498999</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.08371203061469146</v>
+        <v>-0.08406517933885738</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.1366054002162258</v>
+        <v>0.1361981450476932</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>0.07453589122384585</v>
+        <v>0.07414091479677154</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>0.166013388233452</v>
+        <v>0.1662624131832047</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/btc_daily_14days/volume/volume_ratio_30.xlsx
+++ b/workspaces/btc_daily_14days/volume/volume_ratio_30.xlsx
@@ -572,49 +572,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-6.84764803907175</v>
+        <v>-6.772119058238076</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>1.355138193032182</v>
+        <v>1.222939734864049</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>9.5751802308123</v>
+        <v>9.236484004527242</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>6.684238739161962</v>
+        <v>6.966762566576421</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>11.07101905611272</v>
+        <v>11.28048958229085</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>6.444506373257752</v>
+        <v>6.74980049009519</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>5.126936381488783</v>
+        <v>5.484398222571286</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>3.423316351482669</v>
+        <v>3.266711478648368</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>3.363284105857964</v>
+        <v>2.690959297767883</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>6.205277048938939</v>
+        <v>5.479453796582852</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>2.29952686586153</v>
+        <v>1.664972677643078</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>1.793218855122348</v>
+        <v>0.519368364373797</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>1.373629049260117</v>
+        <v>0.1244457727670039</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>1.599709304901943</v>
+        <v>0.3735227305408415</v>
       </c>
     </row>
     <row r="7">
@@ -624,1453 +624,1453 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>4.811056216134148</v>
+        <v>4.742238533303322</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>4.051902251435536</v>
+        <v>4.016402901732619</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>1.93632191644879</v>
+        <v>1.918652893687472</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-3.954992642808804</v>
+        <v>-3.921719378241662</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-8.326305694252625</v>
+        <v>-8.67716804408208</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-2.868306023719107</v>
+        <v>-3.28654420255377</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>1.350216821819139</v>
+        <v>0.9201764448240795</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.884079658028007</v>
+        <v>0.4549556354707107</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-2.621416784797688</v>
+        <v>-2.996449195705196</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.8356077977852721</v>
+        <v>0.4488370313998828</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>4.07770619673817</v>
+        <v>3.661094748018272</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.6656159987237231</v>
+        <v>0.303216459501499</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-3.201621452321071</v>
+        <v>-3.509671562640357</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-2.976706191053395</v>
+        <v>-3.261530302103488</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ 0.6011</t>
+          <t>X ≈ 0.6008</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>158</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-1.211393673480153</v>
+        <v>-0.9417876142666444</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>4.125821759827886</v>
+        <v>4.123567773529999</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>1.83803030145345</v>
+        <v>1.83736869942615</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.7053775278642505</v>
+        <v>0.7048659710199487</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.1681976553935627</v>
+        <v>0.2166738227266976</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>4.886976294175483</v>
+        <v>4.912218570843194</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>1.012335830381154</v>
+        <v>1.060552130904689</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>1.810296002153535</v>
+        <v>1.859499748845487</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>3.014349213883925</v>
+        <v>3.08675413634446</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>1.533377010434201</v>
+        <v>1.632205885550853</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>2.594276888508382</v>
+        <v>2.693358536614149</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>2.628738530606533</v>
+        <v>2.752389878941919</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>2.842205519840753</v>
+        <v>2.990865222443162</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>2.435777440547845</v>
+        <v>2.607776200114799</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ 0.6609</t>
+          <t>X ≈ 0.6605</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>205</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>2.122538910394603</v>
+        <v>2.605028833159771</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-1.445122813525145</v>
+        <v>-1.406750964955251</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.5918839667602924</v>
+        <v>1.119362410830867</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.2531295576416071</v>
+        <v>0.2765637852419687</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.308766516177613</v>
+        <v>0.2751940531974881</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.2288497814917179</v>
+        <v>0.06016820487134567</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>1.634068577643305</v>
+        <v>1.461197140563449</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-1.270437442733382</v>
+        <v>-1.926657659273467</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>1.105000056303538</v>
+        <v>0.4719667681197066</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>3.177379015663583</v>
+        <v>2.572594608731492</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>2.757655240989884</v>
+        <v>1.881828154120271</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>3.279652290504544</v>
+        <v>2.428245350452976</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>1.885315518264385</v>
+        <v>1.058639493733359</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.8152259555617718</v>
+        <v>-1.618836952092671</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ 0.7208</t>
+          <t>X ≈ 0.7203</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.5078672976911562</v>
+        <v>0.267068505064465</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>3.285613405461419</v>
+        <v>3.435665724317495</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.4950208195181744</v>
+        <v>0.2733735147146561</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.1740879192706899</v>
+        <v>-0.3877609437757883</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.085064722580384</v>
+        <v>-0.08413247680901037</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.3838400021639785</v>
+        <v>-0.2084567413827472</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>1.896973655243464</v>
+        <v>1.712163449060611</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>1.428633084083174</v>
+        <v>1.643549059751891</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>2.38736159167437</v>
+        <v>2.795056704687262</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.7390816649394978</v>
+        <v>1.180140374098379</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.9341349572624864</v>
+        <v>1.372929890831742</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.9686006058467385</v>
+        <v>1.431747583494669</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>2.148572141891393</v>
+        <v>2.624124950451687</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>3.975017946877244</v>
+        <v>4.461302420729616</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ 0.7806</t>
+          <t>X ≈ 0.7799</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-5.946720422941162</v>
+        <v>-5.695738795660539</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-1.893121271870619</v>
+        <v>-1.52514896033199</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-1.029055648531632</v>
+        <v>-0.9594167775191451</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.2693224486170109</v>
+        <v>-0.1896697938904026</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>2.341740830216679</v>
+        <v>2.199892916479349</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>2.325184718186833</v>
+        <v>2.472306998321024</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>1.295888905009505</v>
+        <v>1.772579548231455</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.8277166140046504</v>
+        <v>0.9879157160560581</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.1367038591870653</v>
+        <v>0.6306100646973789</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-2.291844977534588</v>
+        <v>-1.792367589922542</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-1.235059324037607</v>
+        <v>-1.036425344107613</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-1.83181316389971</v>
+        <v>-1.618890800995054</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-1.445294724893955</v>
+        <v>-1.37345781546513</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-1.850849561009184</v>
+        <v>-2.086316626889428</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ 0.8404</t>
+          <t>X ≈ 0.8397</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1.461808262329669</v>
+        <v>1.40776931902159</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-2.893465608800291</v>
+        <v>-3.198613100983458</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-3.733645238639305</v>
+        <v>-4.033767332430351</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-2.081295174119411</v>
+        <v>-2.092079410180752</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-1.706451628316053</v>
+        <v>-1.37298997669302</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-2.930493251313806</v>
+        <v>-2.30982972077657</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-4.844288314353768</v>
+        <v>-4.791821193003059</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-3.486429584656925</v>
+        <v>-2.838275540059151</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-2.023242677862086</v>
+        <v>-2.269806584858813</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-4.706025327455976</v>
+        <v>-4.912213126214219</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-4.300451888072324</v>
+        <v>-4.512260214968279</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-3.961921587052572</v>
+        <v>-4.153261548423579</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-3.164219445509552</v>
+        <v>-3.339361160305344</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.9371771750739697</v>
+        <v>-1.101468142040943</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ 0.9003</t>
+          <t>X ≈ 0.8995</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-3.378067299386892</v>
+        <v>-3.529911005602145</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-2.190840293470437</v>
+        <v>-1.906391948750731</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-5.231207690659247</v>
+        <v>-4.923579374616978</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-4.807359961897141</v>
+        <v>-4.795969365257179</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.0565051583527918</v>
+        <v>-0.3277000920891382</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.2419714618662425</v>
+        <v>-0.6382431903444683</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.6114111874133386</v>
+        <v>-0.1156438025125865</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.4431558376440776</v>
+        <v>-1.458433295758461</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-3.444171589351143</v>
+        <v>-4.123034462036308</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.1778909029546014</v>
+        <v>-0.8612462202666222</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.559062649449956</v>
+        <v>-1.649924466746654</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-2.112919791212349</v>
+        <v>-2.177853358967887</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>1.290458767238889</v>
+        <v>1.100311025715229</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-2.013217347240406</v>
+        <v>-2.159416042094165</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ 0.9602</t>
+          <t>X ≈ 0.9591</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>1.414271719349451</v>
+        <v>0.8838453928451173</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-3.337503020318209</v>
+        <v>-4.109961456643596</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.9164743700429909</v>
+        <v>-1.719145398240485</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-1.100280508217878</v>
+        <v>-1.590934438628366</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-1.007749208091887</v>
+        <v>-1.148404818024119</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-1.960432068181895</v>
+        <v>-1.63476026025559</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-3.928226802150668</v>
+        <v>-3.386644538083274</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-4.853110165771653</v>
+        <v>-4.781519088012473</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-5.54118954513001</v>
+        <v>-5.438591396503895</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-6.84394290369206</v>
+        <v>-6.885036208113803</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-5.481245942830142</v>
+        <v>-5.85141916490381</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-5.133388166650363</v>
+        <v>-5.485752216585205</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-5.553539019963637</v>
+        <v>-5.880910143149165</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-2.819966379141562</v>
+        <v>-3.147393231444148</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ 1.02</t>
+          <t>X ≈ 1.019</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>1.161468075425908</v>
+        <v>1.850457233797307</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.2125336379912213</v>
+        <v>0.941156160907255</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.1822377467637395</v>
+        <v>0.5492580183153279</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-1.707641742248377</v>
+        <v>-1.664550592364094</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-1.58367963971493</v>
+        <v>-1.152517986326139</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1.031575184622334</v>
+        <v>1.129224052267475</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.04651265808757898</v>
+        <v>-0.6050553861405419</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.4797961815693057</v>
+        <v>-0.06405886099008029</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>2.405568991934068</v>
+        <v>2.243995796913239</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.09997894346876279</v>
+        <v>-0.2538416883305246</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.02644572608561901</v>
+        <v>0.5467160968713074</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.3919497062554811</v>
+        <v>0.6045391669655231</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.6904528026869912</v>
+        <v>-0.4617596991956177</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>1.853163642241483</v>
+        <v>2.136278451410313</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ 1.08</t>
+          <t>X ≈ 1.079</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>2.217070546646816</v>
+        <v>1.335279007197222</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-3.085390714202205</v>
+        <v>-3.906949668602898</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-3.480162098957244</v>
+        <v>-4.29804254147588</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.3413382124163533</v>
+        <v>-0.1693862506516837</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-3.217085568867262</v>
+        <v>-3.332821743601812</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-3.926422948628229</v>
+        <v>-4.063159838454013</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-3.675562838095658</v>
+        <v>-3.454005976198907</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-1.793638193291756</v>
+        <v>-1.915182822789603</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.847908940418634</v>
+        <v>-1.285262888620359</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-1.026686797151143</v>
+        <v>-1.106750799651813</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-1.56695842520999</v>
+        <v>-1.982079544802694</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.480842545937314</v>
+        <v>0.4148689014271909</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.06069169262382701</v>
+        <v>0.01971097486332241</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.7202840665455739</v>
+        <v>-0.7345886447266992</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ 1.14</t>
+          <t>X ≈ 1.138</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-4.093819256340694</v>
+        <v>-4.368228001064402</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.1750514323538894</v>
+        <v>-0.3928314073237473</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.3518361690660825</v>
+        <v>0.6029053091162595</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.02123181956693543</v>
+        <v>0.7312798602633421</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-1.438716719703812</v>
+        <v>-2.278620337355989</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-5.288808127856747</v>
+        <v>-4.791537792679314</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-3.991030007860253</v>
+        <v>-3.457422043332571</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-3.997269158559575</v>
+        <v>-2.993150864467552</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-5.440739794344928</v>
+        <v>-4.422974960675397</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-4.908170111412112</v>
+        <v>-3.856330837271997</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-6.49535974893498</v>
+        <v>-5.460907909448615</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-6.460981596579657</v>
+        <v>-5.874312089472802</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-6.881132449893066</v>
+        <v>-6.269470016036571</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-5.733737813491373</v>
+        <v>-4.625076316811906</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ 1.2</t>
+          <t>X ≈ 1.198</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>2.849033208044297</v>
+        <v>4.078610620612956</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>3.775918180970287</v>
+        <v>4.934457925701039</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>2.873532583017401</v>
+        <v>3.562110041678324</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>6.557057218991424</v>
+        <v>7.117129491082551</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>3.988310813103858</v>
+        <v>4.67294858761111</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>3.270456416343059</v>
+        <v>2.990560982884126</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>4.708588696670695</v>
+        <v>4.394233167593029</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>5.764362692478031</v>
+        <v>5.882608086649704</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>4.180537896361287</v>
+        <v>4.378893593313705</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>6.376304379219242</v>
+        <v>5.998004806575715</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>6.679217434157081</v>
+        <v>6.086911838802813</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>7.221209799710316</v>
+        <v>7.128423888639425</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>2.232531027615124</v>
+        <v>2.321501256193251</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>1.950652464643689</v>
+        <v>1.590153961345877</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ 1.259</t>
+          <t>X ≈ 1.257</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>3.266210406247261</v>
+        <v>2.679559064956898</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>4.52858753157426</v>
+        <v>3.977568686404986</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>3.559103503141031</v>
+        <v>4.1481612841879</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-2.632510433730275</v>
+        <v>-2.973375583332007</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-3.170799986826069</v>
+        <v>-3.458899913318085</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-5.746989175581817</v>
+        <v>-5.522812473738313</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-4.107561603813416</v>
+        <v>-3.841498634604271</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.5977835455032405</v>
+        <v>1.533172199454924</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-2.336761829410342</v>
+        <v>-1.427777017869012</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.8363078800069275</v>
+        <v>1.585821853431497</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-2.816669140322304</v>
+        <v>-2.123361754609483</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.09127223042388977</v>
+        <v>0.6182759698227471</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1.96997195182319</v>
+        <v>2.56229932980866</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1.620994958371497</v>
+        <v>2.226548870186626</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 1.319</t>
+          <t>X ≈ 1.317</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-4.332767882386293</v>
+        <v>-4.002649138319782</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-3.72173175322785</v>
+        <v>-2.600751596609996</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.153540175019884</v>
+        <v>-1.501952271491874</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>4.902610894494366</v>
+        <v>5.344349680170566</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>3.623580600657959</v>
+        <v>4.108831882502237</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>7.624658333996805</v>
+        <v>8.112960684903257</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>6.058466493249107</v>
+        <v>6.559767282244955</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>6.332138590203108</v>
+        <v>6.093934521861613</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>7.011897174421073</v>
+        <v>7.549499226157657</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>6.902719118831953</v>
+        <v>7.471939302059091</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>3.735054997608799</v>
+        <v>4.282724227657276</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>4.510173890704863</v>
+        <v>5.087159621738678</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>4.830763778132194</v>
+        <v>5.438270351891276</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>3.575017946877246</v>
+        <v>4.19477790047371</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 1.379</t>
+          <t>X ≈ 1.377</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.23091603053421</v>
+        <v>-0.7454059425341057</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>3.407897876401812</v>
+        <v>2.377299325251215</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>3.013126491646851</v>
+        <v>3.160031925171864</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.6433516352350708</v>
+        <v>-0.2394957983192683</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>2.60506208213944</v>
+        <v>1.624196237199335</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>2.902436111774527</v>
+        <v>1.896981756018263</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>5.317725752508295</v>
+        <v>4.189266843263461</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>4.850657108721627</v>
+        <v>4.899904671115344</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>8.539674952198844</v>
+        <v>7.215873238449134</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>11.43975615586892</v>
+        <v>9.921456422340029</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>8.73505499760887</v>
+        <v>7.364374798333351</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>7.519433149964051</v>
+        <v>6.246070947462954</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>5.849282296650777</v>
+        <v>4.674442432663703</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>7.325017946877175</v>
+        <v>6.099957882914495</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 1.439</t>
+          <t>X ≈ 1.437</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-4.288144946197072</v>
+        <v>-6.168648410252693</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-2.284873207935462</v>
+        <v>-4.093288910042773</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-2.679644592690636</v>
+        <v>-3.267514703235591</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-3.754238726210644</v>
+        <v>-4.357142857142925</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-4.292528279306275</v>
+        <v>-4.846391998094845</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-1.585515695454312</v>
+        <v>-2.134582089031952</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1.944231776604823</v>
+        <v>1.463298407108368</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1.477163132818021</v>
+        <v>0.9974656467251748</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-2.198276855030059</v>
+        <v>-2.698043547777615</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>2.975900734182311</v>
+        <v>2.575688847017155</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>2.771199575921919</v>
+        <v>2.371548399481206</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>5.21521628249431</v>
+        <v>4.868739527089993</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>5.999884706289201</v>
+        <v>5.693093795648117</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>6.225620356515932</v>
+        <v>5.942138657663421</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 1.499</t>
+          <t>X ≈ 1.497</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>74</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>4.275840726222405</v>
+        <v>6.949347634572355</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-4.092102123598259</v>
+        <v>-1.390586207340142</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-1.784170805650525</v>
+        <v>-0.4329728443034853</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1.048757040640623</v>
+        <v>2.399613899613897</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-4.894937917860631</v>
+        <v>-3.495040646743355</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.5435098341714877</v>
+        <v>0.8317989261295509</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-6.033625598842981</v>
+        <v>-4.634262568501313</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-6.50069424262972</v>
+        <v>-5.100095328884734</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-5.210325047801184</v>
+        <v>-3.785716586670027</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-4.708892492779661</v>
+        <v>-3.258193816133691</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-7.616296353742477</v>
+        <v>-6.165036966372526</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-2.176512795981822</v>
+        <v>-0.7014648236023078</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-2.596663649295273</v>
+        <v>-1.096622750166055</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-5.073630701771485</v>
+        <v>-3.550280590853347</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 1.559</t>
+          <t>X ≈ 1.556</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>8.630195080576762</v>
+        <v>7.489888175113073</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.3883984198944717</v>
+        <v>-1.366016182770061</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>2.920533899054185</v>
+        <v>1.876609465278818</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-4.356648364764908</v>
+        <v>-7.084415584415588</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.6606176376950046</v>
+        <v>-2.119119270822004</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-2.745712036373618</v>
+        <v>-5.482697388366759</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.8732813080639232</v>
+        <v>-1.906989841228537</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>2.258064516129032</v>
+        <v>-0.5546407834301164</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.3452305077544651</v>
+        <v>-2.409795210748733</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-2.356540140427299</v>
+        <v>-5.051805609745479</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.7093894468356439</v>
+        <v>-3.437764239099849</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-2.526863146332168</v>
+        <v>-5.197779319916727</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-4.798865851497382</v>
+        <v>-7.411119064662316</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-6.424982053122754</v>
+        <v>-8.980256020828868</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 1.619</t>
+          <t>X ≈ 1.616</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>4.661941112322786</v>
+        <v>4.011627305547798</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>17.33646930497325</v>
+        <v>15.47192848126145</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>14.90088159368759</v>
+        <v>15.0781904929468</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>17.07192306380663</v>
+        <v>19.555900621118</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>10.41118453111904</v>
+        <v>10.37099930625298</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>4.58610958116229</v>
+        <v>6.295958738115459</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>10.62384820148796</v>
+        <v>8.409215692368186</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>8.11596323117061</v>
+        <v>5.769469888506656</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>10.09579740117844</v>
+        <v>7.906410322848117</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>3.123429625256747</v>
+        <v>2.734755655076611</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>7.000361120057782</v>
+        <v>6.878441294497094</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>9.075555598943716</v>
+        <v>9.110521075340195</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>10.69622107216097</v>
+        <v>10.88927619225456</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>6.840324069326229</v>
+        <v>6.790494967313478</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 1.678</t>
+          <t>X ≈ 1.675</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.0190839694656475</v>
+        <v>1.148424760478875</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.907897876401826</v>
+        <v>2.004272065566923</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>5.513126491646709</v>
+        <v>6.488582857740084</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.6433516352350708</v>
+        <v>4.179442508710792</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-2.394937917860553</v>
+        <v>1.251168977514979</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-7.097563888225537</v>
+        <v>-3.354094284153902</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-7.182274247491634</v>
+        <v>1.463298407108368</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-12.64934289127844</v>
+        <v>-3.880583133762705</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-17.71032504780108</v>
+        <v>-8.795604523387304</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-13.56024384413101</v>
+        <v>-7.180408713958386</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-11.2649450023912</v>
+        <v>-4.945524771250639</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-13.73056685003588</v>
+        <v>-7.326382424129584</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-11.65071770334936</v>
+        <v>-5.282515960449572</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-6.424982053122825</v>
+        <v>-0.1554223179463321</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 1.738</t>
+          <t>X ≈ 1.735</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>4.27584072622237</v>
+        <v>2.489888175112974</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>8.07006003856398</v>
+        <v>8.406711089957163</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>2.269883248403609</v>
+        <v>0.5129731016423875</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>7.805513797397303</v>
+        <v>3.142857142857068</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.8408838638064964</v>
+        <v>-2.346391998094781</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>4.861895571234072</v>
+        <v>0.4263935207241545</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>10.18259061737324</v>
+        <v>5.365737431498765</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>7.012819270883789</v>
+        <v>2.399904671115273</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>4.249134411658233</v>
+        <v>-0.1370679380214455</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-2.006189790076952</v>
+        <v>-5.960896518836435</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-2.210890948337067</v>
+        <v>-6.165036966372384</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>5.931595312126284</v>
+        <v>1.39312977099236</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>8.214147161515584</v>
+        <v>3.497971844428619</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>11.1425855144449</v>
+        <v>6.247016706443908</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 1.798</t>
+          <t>X ≈ 1.795</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>12.90369935408115</v>
+        <v>12.7072794794609</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.2459482774443345</v>
+        <v>-1.919375866564579</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>3.205434183954466</v>
+        <v>6.38253831903377</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.5104945186109049</v>
+        <v>2.164596273292048</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>6.643523620600988</v>
+        <v>6.023173219296531</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>6.940897650236074</v>
+        <v>6.295958738115459</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>6.856187290969906</v>
+        <v>6.235302648889999</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>6.389118647183281</v>
+        <v>5.769469888506777</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>14.02044418296808</v>
+        <v>14.42814945328289</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>20.86283307894593</v>
+        <v>22.29997304638101</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>24.50428576683952</v>
+        <v>26.44365868580127</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>13.00020238073335</v>
+        <v>13.45834716229678</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>12.58005152741994</v>
+        <v>13.06318923573289</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>12.80578717764642</v>
+        <v>13.31223409774825</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 1.858</t>
+          <t>X ≈ 1.854</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>14.18575063613226</v>
+        <v>13.11488817511302</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-4.092102123598181</v>
+        <v>-4.093288910042837</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>8.846459824980109</v>
+        <v>4.887973101642459</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>5.643351635235142</v>
+        <v>1.892857142857139</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-1.561604584527267</v>
+        <v>-1.721391998094781</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>2.069102778441199</v>
+        <v>1.676393520724147</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>1.98439241917503</v>
+        <v>1.615737431498687</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>4.85065710872167</v>
+        <v>4.274904671115344</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>4.789674952198851</v>
+        <v>4.237932061978547</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>3.939756155868992</v>
+        <v>3.414103481163522</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>3.735054997608749</v>
+        <v>3.209963033627517</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-6.230566850035835</v>
+        <v>-6.106870229007676</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-6.650717703349287</v>
+        <v>-6.502028155571459</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-6.424982053122712</v>
+        <v>-6.252983293556092</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ 1.918</t>
+          <t>X ≈ 1.914</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>24</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-2.480916030534296</v>
+        <v>1.65655484177968</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.07456454306848315</v>
+        <v>4.240044423290499</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.3202068416865558</v>
+        <v>3.846306434975794</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.1899816980981939</v>
+        <v>3.976190476190474</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>7.605062082139504</v>
+        <v>11.82027466857195</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.4308972215588014</v>
+        <v>3.759726854057483</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.5156075808249696</v>
+        <v>3.699070764832022</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.9826762246117653</v>
+        <v>3.23323800444868</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>7.289674952198851</v>
+        <v>11.5295987286452</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-6.060243844130952</v>
+        <v>-1.794229852169771</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>6.235054997608856</v>
+        <v>10.50162970029407</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>2.102766483297394</v>
+        <v>6.393129770992367</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>1.682615629984049</v>
+        <v>5.997971844428541</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-2.25831538645609</v>
+        <v>2.080350039777244</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ 1.978</t>
+          <t>X ≈ 1.974</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>7.519083969465555</v>
+        <v>11.77560246082731</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>12.57456454306848</v>
+        <v>17.33528251852859</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-1.153540175019884</v>
+        <v>2.655830244499697</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>5.643351635235142</v>
+        <v>2.785714285714377</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>18.43839541547278</v>
+        <v>9.439322287619397</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>5.402436111774534</v>
+        <v>-4.573606479275853</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>18.65105908584179</v>
+        <v>9.651451717213078</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>11.51732377538828</v>
+        <v>2.042761813972483</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>4.789674952198851</v>
+        <v>-5.137067938021453</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>3.939756155868899</v>
+        <v>-5.960896518836435</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-2.931611669057958</v>
+        <v>-13.30789410922967</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>10.43609981663078</v>
+        <v>1.035986913849506</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>3.349282296650713</v>
+        <v>-6.502028155571459</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>10.2416846135439</v>
+        <v>0.889873849301047</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X ≈ 2.037</t>
+          <t>X ≈ 2.034</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-8.03647158608991</v>
+        <v>-16.14647546125062</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-20.75876879026469</v>
+        <v>-26.82056163731543</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-21.15354017501989</v>
+        <v>-27.2142996256304</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>1.198907190790855</v>
+        <v>0.1883116883116784</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.6606176376951609</v>
+        <v>8.789971638268987</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.9579916673302478</v>
+        <v>9.062757157087916</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-10.23782980304719</v>
+        <v>-0.0888080230467736</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-10.70489844683393</v>
+        <v>-0.5546407834301164</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0.3452305077545645</v>
+        <v>8.499295698342316</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.5046882885754513</v>
+        <v>7.675467117527198</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>10.40172166427546</v>
+        <v>16.56223576090021</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>10.43609981663078</v>
+        <v>16.6204024982651</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-1.095162147793573</v>
+        <v>7.134335480792309</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>10.2416846135439</v>
+        <v>16.47428943371664</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ 2.097</t>
+          <t>X ≈ 2.094</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>15</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.8524173027989832</v>
+        <v>0.8232215084463519</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>12.57456454306843</v>
+        <v>12.57337775662378</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>12.17979315831349</v>
+        <v>12.17963976830917</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-1.023315031431572</v>
+        <v>-1.023809523809575</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>18.43839541547269</v>
+        <v>18.48694133523846</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>18.73576944510778</v>
+        <v>18.75972685405739</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>18.65105908584161</v>
+        <v>18.69907076483193</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>24.85065710872163</v>
+        <v>24.89990467111534</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>11.45634161886542</v>
+        <v>11.52959872864512</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>17.27308948920238</v>
+        <v>17.37243681449695</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>10.40172166427537</v>
+        <v>10.50162970029405</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>10.43609981663078</v>
+        <v>10.55979643765902</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>16.68261562998396</v>
+        <v>16.83130517776178</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>10.2416846135439</v>
+        <v>10.41368337311057</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 2.157</t>
+          <t>X ≈ 2.153</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>9</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>14.1857506361323</v>
+        <v>14.15655484177967</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>12.57456454306848</v>
+        <v>12.57337775662382</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>34.40201538053558</v>
+        <v>34.40186199053126</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>12.3100183019018</v>
+        <v>12.3095238095238</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>11.7717287488061</v>
+        <v>11.82027466857188</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>23.18021388955232</v>
+        <v>23.20417129850193</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.8732813080638451</v>
+        <v>0.9212929870541657</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>11.51732377538828</v>
+        <v>11.566571337782</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>11.45634161886544</v>
+        <v>11.52959872864513</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>21.71753393364678</v>
+        <v>21.81688125894135</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>21.51283277538673</v>
+        <v>21.6127408114054</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>10.43609981663078</v>
+        <v>10.55979643765902</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>21.1270600744285</v>
+        <v>21.27574962220633</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>21.35279572465503</v>
+        <v>21.52479448422169</v>
       </c>
     </row>
   </sheetData>
@@ -2210,53 +2210,53 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; 0.4515</t>
+          <t>X &gt; 0.4516</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4066</v>
+        <v>4077</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.1545338346286798</v>
+        <v>0.1549248499296425</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.1746953261320812</v>
+        <v>0.174258167482229</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.1366241615020627</v>
+        <v>0.1362607728753389</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.1330474154117809</v>
+        <v>0.132702995560841</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.07438723551368298</v>
+        <v>0.07284441893899896</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.09070317117561899</v>
+        <v>0.08979621350260913</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.1667313994516491</v>
+        <v>0.1649538859551001</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.1306178159907887</v>
+        <v>0.1289029566896787</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.05865063384955249</v>
+        <v>0.0564646440461658</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.05769227380510955</v>
+        <v>0.05478591194033555</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.08406517933885738</v>
+        <v>-0.08660559382350641</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.01129448032103397</v>
+        <v>-0.01469077325867119</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.0003764692595211727</v>
+        <v>-0.003744683281126981</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.09247982587380221</v>
+        <v>0.08746311311548283</v>
       </c>
     </row>
     <row r="7">
@@ -2266,1505 +2266,1505 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3985</v>
+        <v>3994</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.2968617472434261</v>
+        <v>0.2988769391579567</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.1507013807822943</v>
+        <v>0.1524653357114047</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.05522603714640439</v>
+        <v>-0.05285252913445504</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.0001135625615518165</v>
+        <v>-0.009316770186345025</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.1491327588322449</v>
+        <v>-0.1600635801992567</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.03844565175251802</v>
+        <v>-0.04860647927585404</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.06590916518689482</v>
+        <v>0.05440959954069058</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.06368969017526638</v>
+        <v>0.06369561885227881</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.00852008415111527</v>
+        <v>0.001716758152596753</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.06726490732057755</v>
+        <v>-0.05794504309856308</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.1325146035951192</v>
+        <v>-0.1230054427297915</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.04797342139278982</v>
+        <v>-0.0257891479265453</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.02753656938039484</v>
+        <v>-0.006408631165953693</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.06184354286219218</v>
+        <v>0.08151845907284638</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; 0.5711</t>
+          <t>X &gt; 0.571</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3869</v>
+        <v>3877</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.1615175863772222</v>
+        <v>0.1647852944545818</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.03373593725793</v>
+        <v>0.03585953348687809</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.1149364436124358</v>
+        <v>-0.1123485658819874</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.1184612560759959</v>
+        <v>0.1087516087516107</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.09603448348069321</v>
+        <v>0.0969653654479643</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.04639896007174826</v>
+        <v>0.04910791680965332</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.02740317186320596</v>
+        <v>0.02828251135442628</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.03909283407009667</v>
+        <v>0.05188818476810297</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.06981954295537207</v>
+        <v>0.09219532833608923</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.09433475322191498</v>
+        <v>-0.07323869868698551</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.2587450540574352</v>
+        <v>-0.2372019148261302</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.06936819335802369</v>
+        <v>-0.03571787015225425</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.06762854988069478</v>
+        <v>0.09931274179832172</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.1529450598263224</v>
+        <v>0.1824048931862379</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; 0.631</t>
+          <t>X &gt; 0.6307</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3711</v>
+        <v>3719</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.2199708278370593</v>
+        <v>0.2117975341905165</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.1404892203723733</v>
+        <v>-0.1378048660632203</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.1980861999369807</v>
+        <v>-0.1951814047953135</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.0934726355040354</v>
+        <v>0.08342596496607513</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.09296205525050283</v>
+        <v>0.0918796068434915</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.1596940657402612</v>
+        <v>-0.1574990967255161</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.01453144415560814</v>
+        <v>-0.01557298740571866</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.03631813347428903</v>
+        <v>-0.02490735895984386</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.05554712047947419</v>
+        <v>-0.03502712169493094</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.1636364127901331</v>
+        <v>-0.1456937253902879</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.3802156730079602</v>
+        <v>-0.3617054241909017</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.1842431225917665</v>
+        <v>-0.1541693421492596</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.0505021861079058</v>
+        <v>-0.02353353191553964</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.05575090295377549</v>
+        <v>0.07936411166036095</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; 0.6908</t>
+          <t>X &gt; 0.6904</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3506</v>
+        <v>3514</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.1087254037285916</v>
+        <v>0.07218102414820038</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.06420573874193991</v>
+        <v>-0.06377699176815099</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.2442766974192807</v>
+        <v>-0.2718693621667896</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.1137388789709064</v>
+        <v>0.07215867607690285</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.1164516037795309</v>
+        <v>0.0811853946913601</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.155650448589931</v>
+        <v>-0.1701973883667591</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.1109270529601645</v>
+        <v>-0.1017249157590641</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.0358422939068106</v>
+        <v>0.08603709509943513</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.1234056975589155</v>
+        <v>-0.06460416990550755</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.358989568190303</v>
+        <v>-0.3042734375402461</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.5636907264504956</v>
+        <v>-0.492588857188565</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.3867812171966492</v>
+        <v>-0.3048224474376724</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.1636917552454875</v>
+        <v>-0.08666542441925174</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.1066779582862623</v>
+        <v>0.1784338948332049</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; 0.7507</t>
+          <t>X &gt; 0.7501</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3256</v>
+        <v>3262</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.0780787595361403</v>
+        <v>0.05712533892720018</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.3214092971113587</v>
+        <v>-0.3341202058863573</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.3010409416558844</v>
+        <v>-0.3139911294795183</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.1358386024231208</v>
+        <v>0.1076889471384845</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.1188615301615314</v>
+        <v>0.09395673240383928</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.1970732411846754</v>
+        <v>-0.1672417301938509</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.2650963333812086</v>
+        <v>-0.2418536306378343</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.07109803089174704</v>
+        <v>-0.0342857176204987</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.3161857412654001</v>
+        <v>-0.2855221773847845</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.44330093437042</v>
+        <v>-0.4189491826453775</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.6786957697331317</v>
+        <v>-0.6367061853618097</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.4908492318652193</v>
+        <v>-0.4389780721448915</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.3412304451362118</v>
+        <v>-0.2960827065981206</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.1903383184790215</v>
+        <v>-0.1524314848497781</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; 0.8105</t>
+          <t>X &gt; 0.8098</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2939</v>
+        <v>2950</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.7279124923858546</v>
+        <v>0.6655638507886863</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.151884732293837</v>
+        <v>-0.2081537749077071</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.2225174091347384</v>
+        <v>-0.2457291626360103</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.1795391989456476</v>
+        <v>0.1391384139862808</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.1208978227195416</v>
+        <v>-0.1287727894373631</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.469123521252989</v>
+        <v>-0.4464075618198322</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.4334639143849017</v>
+        <v>-0.4549055465046905</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.1680440133456997</v>
+        <v>-0.14239651331782</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.3650343303580996</v>
+        <v>-0.3824148077338094</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.2439173135187573</v>
+        <v>-0.2736927273672407</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.6186864989898453</v>
+        <v>-0.5944308031486898</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.3462131085392812</v>
+        <v>-0.314187302178361</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.222146274777856</v>
+        <v>-0.1821365933891457</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.01123588095535411</v>
+        <v>0.05210145220662099</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; 0.8704</t>
+          <t>X &gt; 0.8696</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2611</v>
+        <v>2620</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.6357187687008334</v>
+        <v>0.5720799559349317</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.192519146485985</v>
+        <v>0.1685071325751224</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.2185587793284895</v>
+        <v>0.2313901488266339</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.4635505640798314</v>
+        <v>0.4201696666485404</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.07828319920142235</v>
+        <v>0.02794158911009248</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.1599204299240142</v>
+        <v>-0.2117017173710849</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.1206342867601791</v>
+        <v>0.0913471875962486</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.2488194364398524</v>
+        <v>0.1971607686763193</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.1567262729160035</v>
+        <v>-0.1446898892409649</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.3166232565966851</v>
+        <v>0.3105483915714942</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.1561744164088168</v>
+        <v>-0.100963739827904</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.1080007485853329</v>
+        <v>0.169360217386874</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.1474439205496054</v>
+        <v>0.2155290963369438</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.1050830560308285</v>
+        <v>0.1973983858332247</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; 0.9302</t>
+          <t>X &gt; 0.9293</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2271</v>
+        <v>2278</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>1.236637862998421</v>
+        <v>1.187918809686316</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.5493409032385941</v>
+        <v>0.4800152475063939</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1.034463931154036</v>
+        <v>1.00531445831642</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>1.252678516009453</v>
+        <v>1.203277458093567</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.09846287404441512</v>
+        <v>0.08133467733228628</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.2200891851898348</v>
+        <v>-0.1476643232723518</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.04715822061218944</v>
+        <v>0.1224230956810644</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.3524176721019145</v>
+        <v>0.4457179109224541</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.3354496000861786</v>
+        <v>0.4525857226536871</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.3906588419103869</v>
+        <v>0.4864719022162021</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.05385728734899686</v>
+        <v>0.1315843587700769</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.4405031631741565</v>
+        <v>0.521751368885262</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.02368115557297301</v>
+        <v>0.08269528604398602</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.4222218218222054</v>
+        <v>0.5512309294465467</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; 0.9901</t>
+          <t>X &gt; 0.989</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1952</v>
+        <v>1956</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>1.207608559629584</v>
+        <v>1.237975885464884</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>1.184537220664112</v>
+        <v>1.235624909437014</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1.353290426073016</v>
+        <v>1.4538196085267</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1.63720409425153</v>
+        <v>1.66326530612244</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.279242410008294</v>
+        <v>0.2837764551977102</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.06432135767617808</v>
+        <v>0.09714390357253677</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.6968241131641122</v>
+        <v>0.7000916938774466</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>1.203116125115066</v>
+        <v>1.306234431197019</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>1.295822493182463</v>
+        <v>1.422401178874928</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>1.572952877180469</v>
+        <v>1.69998192855887</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.9584156533465062</v>
+        <v>1.116516431685724</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>1.351400363078874</v>
+        <v>1.510716683057808</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.8800200015687452</v>
+        <v>1.064434012117701</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.9520671272051118</v>
+        <v>1.160104641004231</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; 1.05</t>
+          <t>X &gt; 1.049</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1650</v>
+        <v>1658</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1.216053666435343</v>
+        <v>1.127891783050487</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1.362443330947272</v>
+        <v>1.288551138062999</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1.634338612858897</v>
+        <v>1.61640064223176</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>2.249412241295744</v>
+        <v>2.26138903214715</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.620213597290963</v>
+        <v>0.5419282908877605</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.1127154033769884</v>
+        <v>-0.08835662978759018</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.8328772676598817</v>
+        <v>0.9346718083800809</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1.335505593570112</v>
+        <v>1.552523575389877</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>1.092705255229149</v>
+        <v>1.274732182387943</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>1.879150095262929</v>
+        <v>2.051151673934648</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>1.128994391548197</v>
+        <v>1.218929278353208</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>1.527008907539887</v>
+        <v>1.673588154587058</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>1.167464114832526</v>
+        <v>1.338743858903811</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.7871391589984569</v>
+        <v>0.9846524121133839</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; 1.11</t>
+          <t>X &gt; 1.108</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1352</v>
+        <v>1359</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.9954153304123992</v>
+        <v>1.082263541681925</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>2.342809119005366</v>
+        <v>2.431637776174178</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>2.761647201705948</v>
+        <v>2.917665183753897</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>2.669978854170054</v>
+        <v>2.796195367361904</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.466008827701579</v>
+        <v>1.3944303220227</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.7278798987567896</v>
+        <v>0.7861585721191489</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>1.826601492153337</v>
+        <v>1.90024550785698</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>2.025213321739372</v>
+        <v>2.315470016196109</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>1.520444182968077</v>
+        <v>1.837968772698076</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>2.519637812673722</v>
+        <v>2.745936692037915</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>1.723220678082171</v>
+        <v>1.923198327745126</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>1.757598830437495</v>
+        <v>1.950524914480219</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>1.411412474165509</v>
+        <v>1.628950505208529</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>1.1193966451021</v>
+        <v>1.362910746179004</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; 1.17</t>
+          <t>X &gt; 1.168</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1135</v>
+        <v>1144</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1.968423176514101</v>
+        <v>2.106612913788972</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>2.824197435873181</v>
+        <v>2.962460218877027</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>3.222377592968371</v>
+        <v>3.352694355997862</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>3.176391282812233</v>
+        <v>3.1842695229792</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>2.02136164161081</v>
+        <v>2.084732674965373</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1.878207036884668</v>
+        <v>1.834414444874106</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>2.9388711269577</v>
+        <v>2.907149811620748</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>3.176648298148947</v>
+        <v>3.313156632754399</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>2.851348961009421</v>
+        <v>3.014632149162502</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>3.939756155868992</v>
+        <v>3.98674746022116</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>3.29452636324757</v>
+        <v>3.310945566378564</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>3.328904515602893</v>
+        <v>3.421101798964401</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>2.996859389161727</v>
+        <v>3.113356459813154</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>2.429643497538031</v>
+        <v>2.488275447702648</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; 1.229</t>
+          <t>X &gt; 1.228</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>938</v>
+        <v>940</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1.78347629355946</v>
+        <v>1.678647454010154</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>2.624315786849579</v>
+        <v>2.534494759098202</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>3.295642483117994</v>
+        <v>3.307246696552319</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>2.466379353785257</v>
+        <v>2.330755232029112</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.608260376382518</v>
+        <v>1.523034753497576</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.585804981710567</v>
+        <v>1.583506047263427</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>2.56719270346786</v>
+        <v>2.584421083303354</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>2.633173100192842</v>
+        <v>2.755530998079252</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>2.572190943670066</v>
+        <v>2.718558388942455</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>3.428029076977737</v>
+        <v>3.550261823352727</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>2.583669070103461</v>
+        <v>2.708501822150325</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>2.511437414356443</v>
+        <v>2.616534026311513</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>3.157384642066496</v>
+        <v>3.285205886981736</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>2.530241827474264</v>
+        <v>2.683186919209867</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; 1.289</t>
+          <t>X &gt; 1.287</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>764</v>
+        <v>769</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1.445785540146268</v>
+        <v>1.45607803207011</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>2.190620389490817</v>
+        <v>2.213603157577445</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>3.235639580652013</v>
+        <v>3.120255286297855</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>3.627644828952413</v>
+        <v>3.510217350919561</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>2.696685118788665</v>
+        <v>2.630851174857106</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>3.255839253135797</v>
+        <v>3.163714717083053</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>4.087359260361765</v>
+        <v>4.013331709782172</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>3.09673040715095</v>
+        <v>3.027342902584785</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>3.69019851240828</v>
+        <v>3.640565351965542</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>4.018290187282602</v>
+        <v>3.987087876482164</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>3.81358902902241</v>
+        <v>3.782947428946073</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>3.062626867241605</v>
+        <v>3.060880096089903</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>3.427816328064324</v>
+        <v>3.44595623974714</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>2.737321611798713</v>
+        <v>2.784728019837921</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 1.349</t>
+          <t>X &gt; 1.347</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>2.686015606985528</v>
+        <v>2.60799841133349</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>3.459567192777016</v>
+        <v>3.229545735626459</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>4.177673391487801</v>
+        <v>4.095650266996792</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>3.354003463534028</v>
+        <v>3.123172103487057</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>2.497748886590955</v>
+        <v>2.318962332613879</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>2.318175380454974</v>
+        <v>2.119306906550918</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>3.664307628502009</v>
+        <v>3.475973651971131</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>2.402326425096824</v>
+        <v>2.380219631745263</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>2.977274316268804</v>
+        <v>2.815687967490355</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>3.399215615328451</v>
+        <v>3.251701906360417</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>3.830444504763015</v>
+        <v>3.677482718666852</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>2.751945073652522</v>
+        <v>2.633287251307323</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>3.126706779957551</v>
+        <v>3.025530899546645</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>2.557529870565645</v>
+        <v>2.487174186758864</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 1.409</t>
+          <t>X &gt; 1.407</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>3.256788887498431</v>
+        <v>3.126251811476656</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>3.467096419206918</v>
+        <v>3.361256544502623</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>4.347370571792496</v>
+        <v>4.240245828915185</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>3.74899826547194</v>
+        <v>3.642857142857132</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>2.482111262467313</v>
+        <v>2.426335274632493</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>2.233037204670708</v>
+        <v>2.153666247996874</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>3.423372382745164</v>
+        <v>3.36573743149868</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>2.045556926572267</v>
+        <v>1.990813762024437</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>2.166724132526717</v>
+        <v>2.135659334705821</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>2.227552148583023</v>
+        <v>2.220921662981745</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>3.115747165186207</v>
+        <v>3.107690306354755</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>2.057229142678153</v>
+        <v>2.074947952810547</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>2.729974464228121</v>
+        <v>2.770699117155822</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>1.862813939591277</v>
+        <v>1.928834888262088</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 1.469</t>
+          <t>X &gt; 1.467</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>4.600629033843326</v>
+        <v>4.754845440070277</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>4.491588863526275</v>
+        <v>4.667394850640925</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>5.598963401518027</v>
+        <v>5.555708144377498</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>5.085411721072056</v>
+        <v>5.044566544566543</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>3.688753069263903</v>
+        <v>3.700616548913771</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>2.913165725508435</v>
+        <v>2.905025999356624</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>3.686824464954718</v>
+        <v>3.699070764832022</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>2.146794447777424</v>
+        <v>2.164861936072604</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>2.944181389967092</v>
+        <v>2.982590181636674</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>2.094262593637232</v>
+        <v>2.158761600821691</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>3.177115083445713</v>
+        <v>3.236672435336878</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>1.494755038376141</v>
+        <v>1.585437463300053</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>2.147565558453287</v>
+        <v>2.258655605112303</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>1.085747560611146</v>
+        <v>1.225649185076385</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 1.529</t>
+          <t>X &gt; 1.526</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>4.661941112322786</v>
+        <v>4.342680053285612</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>6.111979509054883</v>
+        <v>5.805188247317574</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>6.992718328381471</v>
+        <v>6.680485791997789</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>5.847433267888206</v>
+        <v>5.541334300217549</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>5.309143714792512</v>
+        <v>5.05208515926563</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>3.565701417896982</v>
+        <v>3.294413825292672</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>5.521807385161431</v>
+        <v>5.264214588859097</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>3.779228537293058</v>
+        <v>3.529346295480828</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>4.483552503219265</v>
+        <v>4.253795006140983</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>3.378531666073073</v>
+        <v>3.176159318727024</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>5.21464683434349</v>
+        <v>5.002475723982805</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>2.187800496902895</v>
+        <v>2.014957182159883</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>3.043159847671127</v>
+        <v>2.888834788590977</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>2.248487334632351</v>
+        <v>2.122651224210401</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 1.589</t>
+          <t>X &gt; 1.586</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>4.027959709110618</v>
+        <v>3.832071065968471</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>7.15050142669768</v>
+        <v>6.968657992612023</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>7.643304006439678</v>
+        <v>7.45987575650971</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>7.477671161862368</v>
+        <v>7.58975979772439</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>6.051807644269623</v>
+        <v>6.215554904560079</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>4.574033744910629</v>
+        <v>4.718428918954238</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>6.264471314638541</v>
+        <v>6.427684334153547</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>4.022254741857722</v>
+        <v>4.191940069345435</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>5.144704537997669</v>
+        <v>5.334908463158484</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>4.294785741667809</v>
+        <v>4.511079882343502</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>6.161090500567376</v>
+        <v>6.371836189969663</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>2.941030783100217</v>
+        <v>3.185165169222458</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>4.296027858780889</v>
+        <v>4.559918747083401</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>3.634189544510377</v>
+        <v>3.924007856886391</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 1.648</t>
+          <t>X &gt; 1.646</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>3.920468052510628</v>
+        <v>3.803881349174453</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>5.423468810657873</v>
+        <v>5.633673547295047</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>6.412780470885536</v>
+        <v>6.263826343963281</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>5.850964091982547</v>
+        <v>5.711116528522673</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>5.312674538886853</v>
+        <v>5.563164315898391</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>4.571986284784913</v>
+        <v>4.470762121406743</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>5.525338209255771</v>
+        <v>6.116590673819509</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>3.328165759240655</v>
+        <v>3.94427327179794</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>4.305245886454905</v>
+        <v>4.931191447644082</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>4.493389373862065</v>
+        <v>4.789956723484387</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>6.018792021830251</v>
+        <v>6.292300917586516</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>1.900921039237481</v>
+        <v>2.254904515019675</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>3.210873992152436</v>
+        <v>3.566231230094075</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>3.0905888811333</v>
+        <v>3.473979163781792</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 1.708</t>
+          <t>X &gt; 1.705</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>4.547196419264843</v>
+        <v>4.235919921144763</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>6.148861731823509</v>
+        <v>6.224171407417479</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>6.557303198474095</v>
+        <v>6.227258815928167</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>6.687528342062457</v>
+        <v>5.960317460317455</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>6.550845214669565</v>
+        <v>6.264719113016334</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>6.446612818601849</v>
+        <v>5.743853838184464</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>7.566721736444109</v>
+        <v>6.8736739394352</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>5.894833815548942</v>
+        <v>5.21736498857566</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>7.841883787540212</v>
+        <v>7.164519363565852</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>7.393571416913169</v>
+        <v>6.737516179576261</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>8.79529596146422</v>
+        <v>8.120677319341766</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>4.412003431088621</v>
+        <v>3.813764691627284</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>5.598278280586456</v>
+        <v>5.005908352365054</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>4.619194653704561</v>
+        <v>4.064477023904224</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 1.768</t>
+          <t>X &gt; 1.765</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>212</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>4.594555667578859</v>
+        <v>4.565359873226228</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>5.813558253760313</v>
+        <v>5.812371467315657</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>7.305579321835459</v>
+        <v>7.305425931831138</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>6.492408239008732</v>
+        <v>6.491913746630729</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>7.840911138743223</v>
+        <v>7.889457058508995</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>6.723190828755662</v>
+        <v>6.747148237705275</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>7.110178582697046</v>
+        <v>7.158190261687366</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>5.699713712495218</v>
+        <v>5.748961274888934</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>8.468920235217723</v>
+        <v>8.54217734499742</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>9.034095778510505</v>
+        <v>9.133443103805078</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>10.71618707308049</v>
+        <v>10.81609510909917</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>4.146791640530161</v>
+        <v>4.270488261558405</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>5.141735126839393</v>
+        <v>5.290424674617221</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>3.48067832423574</v>
+        <v>3.652677083802402</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 1.828</t>
+          <t>X &gt; 1.825</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>3.433062464089296</v>
+        <v>3.574544259769098</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>6.660586048444834</v>
+        <v>6.753271936518011</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>7.878717889496244</v>
+        <v>7.417735006404364</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>7.471308624482454</v>
+        <v>7.018518518518512</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>8.008287888591063</v>
+        <v>8.116570964868181</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>6.692758692419694</v>
+        <v>6.802054896385521</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>7.145682741755678</v>
+        <v>7.270499336260592</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>5.603345280764643</v>
+        <v>5.746465517676192</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>7.692900758650467</v>
+        <v>7.825895024941509</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>7.380616370922752</v>
+        <v>7.531166973227052</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>8.788818438469008</v>
+        <v>8.91432811299255</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>2.909218096200682</v>
+        <v>3.152389030251619</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>4.101970468693729</v>
+        <v>4.344532690989389</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>2.177168484511661</v>
+        <v>2.477175436602643</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 1.888</t>
+          <t>X &gt; 1.884</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>1.365237815619494</v>
+        <v>1.630015563648044</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>8.728410696914636</v>
+        <v>8.964035930721494</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>7.692613671133962</v>
+        <v>7.933355267247549</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>7.822838814722324</v>
+        <v>8.063239308462229</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>9.848651825729199</v>
+        <v>10.12176086814726</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>7.581923291261717</v>
+        <v>7.846775686329238</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>8.138238573021184</v>
+        <v>8.423062272263017</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>5.748093006157518</v>
+        <v>6.046401486401969</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>8.251213413737311</v>
+        <v>8.557199577902111</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>8.042320258433094</v>
+        <v>8.370313672246368</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>9.760696023249821</v>
+        <v>10.07700125018798</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>4.666869047400013</v>
+        <v>5.039626586278992</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>6.169795117163531</v>
+        <v>6.555296685192872</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>3.831428203287501</v>
+        <v>4.256570846571293</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 1.948</t>
+          <t>X &gt; 1.944</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>2.064538514920187</v>
+        <v>1.625226520977677</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>10.30183727034121</v>
+        <v>9.816485526047394</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>9.149490128010413</v>
+        <v>8.670867838484561</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>9.279715271598775</v>
+        <v>8.800751879699241</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>10.2565772336546</v>
+        <v>9.815262137243558</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>9.038799748138167</v>
+        <v>8.58428825756625</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>9.711665146447757</v>
+        <v>9.275511867588918</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>6.971869229933752</v>
+        <v>6.554040009461204</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>8.426038588562484</v>
+        <v>8.02082679882065</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>10.60642282253565</v>
+        <v>10.20451701499815</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>10.40172166427546</v>
+        <v>10.00037656746206</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>5.133069513600489</v>
+        <v>4.795385410090113</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>6.985645933014347</v>
+        <v>6.655866581270644</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>4.938654310513613</v>
+        <v>4.649272345541654</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 2.007</t>
+          <t>X &gt; 2.004</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>1.365237815619494</v>
+        <v>0.4310646457012552</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>10.01046197896592</v>
+        <v>8.931921173990773</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>10.47039144891173</v>
+        <v>9.378519320129847</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>9.745915737799244</v>
+        <v>9.508403361344527</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>9.20762618470355</v>
+        <v>9.859490354846393</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>9.505000214338637</v>
+        <v>10.13227587366532</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>8.56558900037161</v>
+        <v>9.231283649986075</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>6.389118647183167</v>
+        <v>7.084778620695175</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>8.892239054762953</v>
+        <v>9.568814414919721</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>11.46112367723651</v>
+        <v>12.10633037191987</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>12.11112337367717</v>
+        <v>12.74252605883756</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>4.453193833724804</v>
+        <v>5.23766758611842</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>7.451846399214816</v>
+        <v>8.203854197369715</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>4.258778630637927</v>
+        <v>5.091554521569961</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 2.067</t>
+          <t>X &gt; 2.064</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>108</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>2.148713599095274</v>
+        <v>2.119517804742642</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>12.57456454306848</v>
+        <v>12.57337775662382</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>13.10571908423938</v>
+        <v>13.10556569423505</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>10.45816645004995</v>
+        <v>10.45767195767195</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>9.919876896954257</v>
+        <v>9.968422816720029</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>10.21725092658934</v>
+        <v>10.24120833553896</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>10.13254056732318</v>
+        <v>10.1805522463135</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>7.813620071684589</v>
+        <v>7.862867634078306</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>9.604489767013661</v>
+        <v>9.677746876793357</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>12.45827467438751</v>
+        <v>12.55762199968208</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>12.25357351612732</v>
+        <v>12.35348155214599</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>3.954618335149306</v>
+        <v>4.07831495617755</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>8.164097111465523</v>
+        <v>8.312786659243351</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>3.760203132062429</v>
+        <v>3.932201891629092</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 2.127</t>
+          <t>X &gt; 2.123</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>93</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>2.357793646885</v>
+        <v>2.328597852532369</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>12.57456454306848</v>
+        <v>12.57337775662382</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>13.25506197551774</v>
+        <v>13.25490858551342</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>12.3100183019018</v>
+        <v>12.3095238095238</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>8.545922297193208</v>
+        <v>8.59446821695898</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>8.843296326828295</v>
+        <v>8.867253735777908</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>8.758585967562126</v>
+        <v>8.806597646552447</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>5.065710872162491</v>
+        <v>5.114958434556208</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>9.305803984456915</v>
+        <v>9.379061094236611</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>11.68169163973995</v>
+        <v>11.78103896503453</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>12.55225929868408</v>
+        <v>12.65216733470275</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>2.909218096200682</v>
+        <v>3.032914717228927</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>6.790142511704474</v>
+        <v>6.938832059482301</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>2.714802893113806</v>
+        <v>2.886801652680468</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 2.187</t>
+          <t>X &gt; 2.183</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>1.090512540894217</v>
+        <v>1.061316746541586</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>12.57456454306848</v>
+        <v>12.57337775662382</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>10.98931696783726</v>
+        <v>10.98916357783294</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>12.3100183019018</v>
+        <v>12.3095238095238</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>8.200300177377542</v>
+        <v>8.248846097143314</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>7.307198016536439</v>
+        <v>7.331155425486052</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>9.603440038222658</v>
+        <v>9.651451717212979</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>4.374466632531153</v>
+        <v>4.42371419492487</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>9.075389237913143</v>
+        <v>9.148646347692839</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>10.60642282253565</v>
+        <v>10.70577014783022</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>11.59219785475166</v>
+        <v>11.69210589077034</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>2.102766483297458</v>
+        <v>2.226463104325703</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>5.254044201412619</v>
+        <v>5.402733749190446</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>0.7178750897343846</v>
+        <v>0.889873849301047</v>
       </c>
     </row>
   </sheetData>
@@ -3904,53 +3904,53 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; 0.4515</t>
+          <t>X &lt; 0.4516</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-6.052344601962922</v>
+        <v>-6.081540396315553</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-5.282578314074371</v>
+        <v>-5.283765100519027</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-5.67734969882941</v>
+        <v>-5.677503088833731</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-4.356648364764858</v>
+        <v>-4.357142857142861</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-1.323509346431983</v>
+        <v>-1.274963426666211</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.1643408736793006</v>
+        <v>0.1882982826289137</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-1.110845676063065</v>
+        <v>-1.062833997072744</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.8030380611025834</v>
+        <v>0.8522856234963001</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>6.694436856960756</v>
+        <v>6.767693966740453</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>5.844518060630897</v>
+        <v>5.94386538592547</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>11.59219785475166</v>
+        <v>11.69210589077034</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>9.245623626154604</v>
+        <v>9.369320247182849</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>8.825472772841195</v>
+        <v>8.974162320619023</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>4.289303661162954</v>
+        <v>4.461302420729616</v>
       </c>
     </row>
     <row r="7">
@@ -3960,1505 +3960,1505 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-6.373131599396622</v>
+        <v>-6.356265671040831</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-1.996293740364649</v>
+        <v>-2.022282992883071</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>1.800551641347376</v>
+        <v>1.725990853121743</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>1.065038382223094</v>
+        <v>1.264158918005066</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>4.743616299006916</v>
+        <v>4.916921611372679</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>3.233761412979348</v>
+        <v>3.41455920119752</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>1.944231776604759</v>
+        <v>2.170471159309336</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>2.079572771372234</v>
+        <v>2.042761813972483</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>5.030638807620541</v>
+        <v>4.743171582936625</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>5.987948926953337</v>
+        <v>5.715750187750388</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>6.988067045801571</v>
+        <v>6.70921453063346</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>5.587614968145935</v>
+        <v>4.970974082369615</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>5.167464114832526</v>
+        <v>4.575816155805789</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>2.968957340816644</v>
+        <v>2.42965143698283</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; 0.5711</t>
+          <t>X &lt; 0.571</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-1.77669067842168</v>
+        <v>-1.810811125586284</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.4853626651342182</v>
+        <v>0.4521656354117027</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>1.851154660660868</v>
+        <v>1.806679395348752</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.999757905400898</v>
+        <v>-0.860639360639361</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.639618768924386</v>
+        <v>-0.6505878022905804</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.7215850479447496</v>
+        <v>0.6711487654793871</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>1.700704475912616</v>
+        <v>1.65944372520498</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>1.5882457612039</v>
+        <v>1.391132741290782</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>1.881873533759133</v>
+        <v>1.553072907048971</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>3.86883417005339</v>
+        <v>3.546145734684693</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>5.791792586261273</v>
+        <v>5.454681343486627</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>3.55591001829152</v>
+        <v>3.048059348457151</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>1.712271620494128</v>
+        <v>1.244450717667981</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.514519726236685</v>
+        <v>0.08504487545799577</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; 0.631</t>
+          <t>X &lt; 0.6307</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-1.575938654968745</v>
+        <v>-1.498875869830805</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>1.79025081757829</v>
+        <v>1.762566945813013</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>1.847968120606055</v>
+        <v>1.81927940794877</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.3883943965108898</v>
+        <v>-0.303088803088805</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.3494833724060129</v>
+        <v>-0.3418874935902778</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>2.220617929956354</v>
+        <v>2.183150277480905</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>1.454089388872006</v>
+        <v>1.446818512579775</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>1.668838926903447</v>
+        <v>1.559046883304958</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>2.289674952198844</v>
+        <v>2.10275106650343</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>3.030665246778085</v>
+        <v>2.862632892928275</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>4.644145906699713</v>
+        <v>4.4684471965234</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>3.222736111239747</v>
+        <v>2.942903526648479</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>2.11921395952087</v>
+        <v>1.869012568410447</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>1.205997445738291</v>
+        <v>0.9868357109687906</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; 0.6908</t>
+          <t>X &lt; 0.6904</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.4007927639704008</v>
+        <v>-0.2024195171946701</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.7615188317176944</v>
+        <v>0.7603320452730387</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>1.445329881477285</v>
+        <v>1.599259696403628</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.3443026857525169</v>
+        <v>-0.1198547215496433</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.3354325082778686</v>
+        <v>-0.1468542477095767</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1.439587814560916</v>
+        <v>1.512680115485317</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>1.509676216904658</v>
+        <v>1.452024026259856</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.7330100498980983</v>
+        <v>0.4554602266709011</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>1.910417986254586</v>
+        <v>1.586270547295392</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>3.072883090853516</v>
+        <v>2.771715536804983</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>4.045132516988645</v>
+        <v>3.649491627135973</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>3.241482839405123</v>
+        <v>2.780301332043365</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>2.04493447056376</v>
+        <v>1.612345878431633</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.5625955866287953</v>
+        <v>0.161236180941593</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; 0.7507</t>
+          <t>X &lt; 0.7501</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>894</v>
+        <v>899</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.1475826972010239</v>
+        <v>-0.07108743464308276</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>1.463453431957376</v>
+        <v>1.511594552776252</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>1.179793158313444</v>
+        <v>1.228844355804497</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.2965816239417265</v>
+        <v>-0.1951006817821508</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.2178777842302679</v>
+        <v>-0.1294108660193132</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>1.143796200960708</v>
+        <v>1.031276983543236</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>1.616499442586409</v>
+        <v>1.52555985103254</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.9264653584429183</v>
+        <v>0.7887935600042297</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>2.044139237913143</v>
+        <v>1.926335843958533</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>2.421899013011853</v>
+        <v>2.326089020651885</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>3.176395779731706</v>
+        <v>3.011826214940044</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>2.606122187995446</v>
+        <v>2.402584720936751</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>2.074114511415814</v>
+        <v>1.89619208914489</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>1.516852398778809</v>
+        <v>1.366594014564036</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; 0.8105</t>
+          <t>X &lt; 0.8098</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>1211</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-1.659897968136981</v>
+        <v>-1.521643950092908</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.5877008320668438</v>
+        <v>0.7294645936669752</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.6034384785104976</v>
+        <v>0.6654875286828599</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.2892695644361751</v>
+        <v>-0.1939112000942202</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.4504568189815501</v>
+        <v>0.4710028906109045</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1.451818827823914</v>
+        <v>1.403310256091004</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>1.531717522055686</v>
+        <v>1.589974859363487</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.9000398247710066</v>
+        <v>0.8404987305212899</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>1.544205429958318</v>
+        <v>1.592907289063596</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>1.188520571025499</v>
+        <v>1.264537007175122</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>2.020298196289758</v>
+        <v>1.968736774337636</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>1.442700476696793</v>
+        <v>1.366292446467178</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>1.152750504743203</v>
+        <v>1.05371090305777</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.6352987065799667</v>
+        <v>0.4769919335289572</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; 0.8704</t>
+          <t>X &lt; 0.8696</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1539</v>
+        <v>1541</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.9951279168392659</v>
+        <v>-0.8930354988843945</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.1515336481459784</v>
+        <v>-0.1127063857709913</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.3175134566402278</v>
+        <v>-0.341949178150287</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.6697143414789579</v>
+        <v>-0.6006661732050347</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.008206526274790349</v>
+        <v>0.07588779465132944</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.519016422655362</v>
+        <v>0.6077406709832118</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.1752387058762395</v>
+        <v>0.2232503848665601</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.03276258039754509</v>
+        <v>0.05220538401229646</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.7844902470789563</v>
+        <v>0.7643587805258889</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.06542854925090325</v>
+        <v>-0.05946980028909366</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.6740952051314935</v>
+        <v>0.57945071196729</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.2911722803989036</v>
+        <v>0.1836615479054657</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.2323991797675902</v>
+        <v>0.1127578366464377</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.3001641457076545</v>
+        <v>0.138969983536704</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; 0.9302</t>
+          <t>X &lt; 0.9293</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1879</v>
+        <v>1883</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-1.422714972333296</v>
+        <v>-1.371943481848334</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.5187829070815013</v>
+        <v>-0.4386278930936811</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-1.20297520326848</v>
+        <v>-1.174891233280697</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-1.415471894176619</v>
+        <v>-1.362972215913395</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.01688913737274333</v>
+        <v>0.002574615577721318</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.4687491091220153</v>
+        <v>0.3813484756791041</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.2540314849924457</v>
+        <v>0.1617098745299614</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.1068800462677544</v>
+        <v>-0.2220465483968468</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.02068929101987749</v>
+        <v>-0.1238053385519606</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.08573508151815901</v>
+        <v>-0.2049283490751606</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.270655422688499</v>
+        <v>0.1744855800465714</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.1433791839008478</v>
+        <v>-0.2448012634903947</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.4237503817570882</v>
+        <v>0.2920270461270533</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.1184360179976807</v>
+        <v>-0.2784745309432424</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; 0.9901</t>
+          <t>X &lt; 0.989</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2198</v>
+        <v>2205</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-1.0109929188202</v>
+        <v>-1.041517157015313</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.9246813091185402</v>
+        <v>-0.973939904617886</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-1.159576088706316</v>
+        <v>-1.253196052586397</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-1.367517929982256</v>
+        <v>-1.394682431995868</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.1600036179058648</v>
+        <v>-0.1652522423281653</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.1168513429622067</v>
+        <v>0.08702700488704096</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.3512084878544499</v>
+        <v>-0.3563087432410157</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.7936260128754711</v>
+        <v>-0.8881388071455234</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.7845420246508965</v>
+        <v>-0.9005477749040978</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-1.06478517019822</v>
+        <v>-1.180651842805624</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.5629913449627608</v>
+        <v>-0.7051366491999005</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.866930486399518</v>
+        <v>-1.009452920443977</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.4433507183561076</v>
+        <v>-0.6090091165868685</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.5105143552155624</v>
+        <v>-0.6974277380005347</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; 1.05</t>
+          <t>X &lt; 1.049</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2500</v>
+        <v>2503</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.7499172243266372</v>
+        <v>-0.6980847440427027</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.7879619962096456</v>
+        <v>-0.7466753642260997</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-1.042030816198704</v>
+        <v>-1.039438217608236</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-1.408441193450116</v>
+        <v>-1.427688891419464</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.3313667739785231</v>
+        <v>-0.2828208542127513</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.2269975152833084</v>
+        <v>0.2110825159394594</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.3145040041729317</v>
+        <v>-0.3861572633557273</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.6401649184132552</v>
+        <v>-0.7904385052613492</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.3999458062841796</v>
+        <v>-0.5262894949076795</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.9484227578690252</v>
+        <v>-1.070676957958199</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.4918726891670744</v>
+        <v>-0.5562545312427787</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.7149793200598609</v>
+        <v>-0.8174490713230043</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.473188714944655</v>
+        <v>-0.5914850245810399</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.2249820531227513</v>
+        <v>-0.3600548077390755</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; 1.11</t>
+          <t>X &lt; 1.108</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2798</v>
+        <v>2802</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.4353806338783599</v>
+        <v>-0.4816420739972997</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-1.031603902957606</v>
+        <v>-1.085100942794703</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-1.300686253102235</v>
+        <v>-1.388736300066945</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-1.222745230861719</v>
+        <v>-1.294464794464801</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.6377238102723837</v>
+        <v>-0.6085002602030372</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.2140998825233993</v>
+        <v>-0.2451419263723977</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.671579060325854</v>
+        <v>-0.7140915064913358</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.7627523063996264</v>
+        <v>-0.9111470222892919</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.4475708558639369</v>
+        <v>-0.6078240007889235</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.9567463423465696</v>
+        <v>-1.075019200719467</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.6062516785782748</v>
+        <v>-0.7085462388404338</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.5877097071787389</v>
+        <v>-0.6860428395639815</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.4163482857001313</v>
+        <v>-0.5262878772981807</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.2777340188125308</v>
+        <v>-0.4000211236774334</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; 1.17</t>
+          <t>X &lt; 1.168</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3015</v>
+        <v>3017</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.6975606804682997</v>
+        <v>-0.7586247131883681</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.9701992494653737</v>
+        <v>-1.035437670373419</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-1.182180844770933</v>
+        <v>-1.246286157616794</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-1.133507868897084</v>
+        <v>-1.149470899470906</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.6952024681250961</v>
+        <v>-0.727966592868178</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.5783776493898714</v>
+        <v>-0.5696355990640711</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.9099380463003683</v>
+        <v>-0.9103300958101528</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.9950893328540147</v>
+        <v>-1.060360229546909</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.8063515378673713</v>
+        <v>-0.8806916544838543</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.240767196234351</v>
+        <v>-1.273914074318384</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.029689866539641</v>
+        <v>-1.047448360874014</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-1.010149216625209</v>
+        <v>-1.055528725198428</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.881486934118513</v>
+        <v>-0.9354277579571431</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.6704215224428225</v>
+        <v>-0.7011105723098154</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; 1.229</t>
+          <t>X &lt; 1.228</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3212</v>
+        <v>3221</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.4809160305343525</v>
+        <v>-0.4519255048622242</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.6801914536229958</v>
+        <v>-0.6567564023028964</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.9342827543972803</v>
+        <v>-0.9410374279332601</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.6632902021329485</v>
+        <v>-0.6253373446002755</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.4087535030825364</v>
+        <v>-0.3854254553438494</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.3429055031323003</v>
+        <v>-0.3436715551977585</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.5660890968237311</v>
+        <v>-0.5735062138825882</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.58128819892287</v>
+        <v>-0.6194751738458919</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.5009685044377648</v>
+        <v>-0.5464972184184731</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.7741741923897081</v>
+        <v>-0.8120131441466043</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.5573244736198149</v>
+        <v>-0.5956916359350473</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.5056135208510639</v>
+        <v>-0.5375248985701546</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.6905558608345004</v>
+        <v>-0.7292162375081475</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.5096644939695736</v>
+        <v>-0.5559947806718952</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; 1.289</t>
+          <t>X &lt; 1.287</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3386</v>
+        <v>3392</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.2890949066743929</v>
+        <v>-0.2927843652687727</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.4134676327211935</v>
+        <v>-0.4211384987619837</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.704124023513657</v>
+        <v>-0.6815611328565154</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.7641866450946537</v>
+        <v>-0.7416225749559118</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.5503134701433225</v>
+        <v>-0.5388353970950774</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.619956345503013</v>
+        <v>-0.6030182439817366</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.7477030715411459</v>
+        <v>-0.7360572139852763</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.5208051554293149</v>
+        <v>-0.5091594842701781</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.5951672772319938</v>
+        <v>-0.5889372344594861</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.6915122807091834</v>
+        <v>-0.6899895694842542</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.6733250555042147</v>
+        <v>-0.6716643595978553</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.4749588217005751</v>
+        <v>-0.4792921500447491</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.5538768412294175</v>
+        <v>-0.5633308375638038</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.4001740200453767</v>
+        <v>-0.4157191426126943</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 1.349</t>
+          <t>X &lt; 1.347</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3521</v>
+        <v>3526</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.4435645874104139</v>
+        <v>-0.4332539554323347</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.5398802158710296</v>
+        <v>-0.5036902667415433</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.72130159442343</v>
+        <v>-0.7126418262625407</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.5475291350848792</v>
+        <v>-0.5109890109890145</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.3906886260758498</v>
+        <v>-0.3626579104003014</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.3045630381262825</v>
+        <v>-0.2725312104586521</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.4872629096231549</v>
+        <v>-0.4593404060331636</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.2585008158601738</v>
+        <v>-0.2586457252606493</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.3039155185895765</v>
+        <v>-0.280086912816131</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.4006693760459044</v>
+        <v>-0.3801599749270892</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.5044455699280945</v>
+        <v>-0.4835407918188253</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.2839304605950588</v>
+        <v>-0.2678679614339288</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.3474809060750061</v>
+        <v>-0.3353142343919941</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.2477596731170806</v>
+        <v>-0.2405045641176358</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 1.409</t>
+          <t>X &lt; 1.407</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3601</v>
+        <v>3611</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.460993507014706</v>
+        <v>-0.4405754010459262</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.4524674709549501</v>
+        <v>-0.436098736153788</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.638590008906931</v>
+        <v>-0.6217590905165764</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.5211457339146719</v>
+        <v>-0.504615930879396</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.3243007987469753</v>
+        <v>-0.3160052577632868</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.2334741126643678</v>
+        <v>-0.2215755315002212</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.3585491920592645</v>
+        <v>-0.3501276873515096</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.1451843107405324</v>
+        <v>-0.1374190778478876</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.1077182813008761</v>
+        <v>-0.1038820973134875</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.1379137470436262</v>
+        <v>-0.1379366294865036</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.2993512177075104</v>
+        <v>-0.2989605966990325</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.1106667667719279</v>
+        <v>-0.114620021423903</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.2098515178967517</v>
+        <v>-0.2174212895692378</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.07952245856568396</v>
+        <v>-0.09125524038522315</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 1.469</t>
+          <t>X &lt; 1.467</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3684</v>
+        <v>3693</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.5469154895551753</v>
+        <v>-0.567316358076404</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.4936172751133299</v>
+        <v>-0.5170405969524268</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.6844377844019363</v>
+        <v>-0.680331433994688</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.5937896749976659</v>
+        <v>-0.5899270861463677</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.4134865233303628</v>
+        <v>-0.4163541806987752</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.2638694136859243</v>
+        <v>-0.2639604376654816</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.3067662550776475</v>
+        <v>-0.3099382441769905</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.1086924847743092</v>
+        <v>-0.1122607790063128</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.1547544324582404</v>
+        <v>-0.1614054177402195</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.06783603502037749</v>
+        <v>-0.07774802005364023</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.2302284306526587</v>
+        <v>-0.2397122910478515</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.009259520012953715</v>
+        <v>-0.004028551064457986</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.06998500321360268</v>
+        <v>-0.08621873488927889</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.06253151908137511</v>
+        <v>0.04271126371442335</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 1.529</t>
+          <t>X &lt; 1.526</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3758</v>
+        <v>3767</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.4522764123959249</v>
+        <v>-0.4201647349398954</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.5642506647122332</v>
+        <v>-0.5341462797173548</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.7060297832271942</v>
+        <v>-0.6754864007397572</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.5615315919410762</v>
+        <v>-0.5313551949771238</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.5015214060474449</v>
+        <v>-0.4766886082642756</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.2693642068659301</v>
+        <v>-0.2424806514612783</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.4193260403203212</v>
+        <v>-0.3947289172029613</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.2343588317672101</v>
+        <v>-0.2100873776522079</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.2541730414232575</v>
+        <v>-0.2325080228570897</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.1591274166987873</v>
+        <v>-0.1401593138510222</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.3755538830080525</v>
+        <v>-0.3560183987332692</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.03375833939757911</v>
+        <v>-0.01772191380465671</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.1197254181670644</v>
+        <v>-0.1060621258474725</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.03860632135053521</v>
+        <v>-0.02787047168192203</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 1.589</t>
+          <t>X &lt; 1.586</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3812</v>
+        <v>3822</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.3240532854363067</v>
+        <v>-0.3067219943785133</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.5617673955647149</v>
+        <v>-0.5460797290308363</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.6548044526378192</v>
+        <v>-0.6388661887306171</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.6151517661254005</v>
+        <v>-0.625410080524901</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.4850975619327897</v>
+        <v>-0.5002682706084869</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.3043701709479762</v>
+        <v>-0.3177318056466092</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.4010487958027156</v>
+        <v>-0.4164511294832991</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.1991071657676287</v>
+        <v>-0.2150378576202883</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.2456931379242775</v>
+        <v>-0.2637990590039436</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.1902228797704169</v>
+        <v>-0.2107658340481464</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.3802792094685259</v>
+        <v>-0.4003310840195837</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.06905662455081796</v>
+        <v>-0.09222587754319278</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.1859917657673265</v>
+        <v>-0.2111571118884896</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.1290743931017744</v>
+        <v>-0.1566986258428571</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 1.648</t>
+          <t>X &lt; 1.646</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3861</v>
+        <v>3868</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.2609883072509191</v>
+        <v>-0.255538261372422</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.3353244318863275</v>
+        <v>-0.3561755079809856</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.4579478885185111</v>
+        <v>-0.4524819125364559</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.3912647429617024</v>
+        <v>-0.3860237235688544</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.3471343002894969</v>
+        <v>-0.3712823772539267</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.2424333635420837</v>
+        <v>-0.23924115419846</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.2613848989911247</v>
+        <v>-0.311681923340025</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.09374423599003023</v>
+        <v>-0.1439776210890997</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.1146188915673108</v>
+        <v>-0.1667606826638419</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.1482127962655468</v>
+        <v>-0.1757725518942834</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.2866841328259824</v>
+        <v>-0.3138357263828553</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.04693768012202781</v>
+        <v>0.01716077874430511</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.04792122484074213</v>
+        <v>-0.07917987436184148</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.04062566876637419</v>
+        <v>-0.07407946728928749</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 1.708</t>
+          <t>X &lt; 1.705</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3901</v>
+        <v>3909</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.2581260458639392</v>
+        <v>-0.2408614424290505</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.3226157959723253</v>
+        <v>-0.3314934497010853</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.3968939582509705</v>
+        <v>-0.3798840412146873</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.3806831384800162</v>
+        <v>-0.3382604891918533</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.3680836979117004</v>
+        <v>-0.3543041981968784</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.312580516519148</v>
+        <v>-0.2718449270675265</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.3322230704189693</v>
+        <v>-0.2930981149773118</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.2222888856474583</v>
+        <v>-0.1831093774159456</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.2948104548672035</v>
+        <v>-0.2571496958139932</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.2855959568070645</v>
+        <v>-0.2491663885016564</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.3991663138666084</v>
+        <v>-0.3623784796649545</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.09426144393800229</v>
+        <v>-0.05982343790561373</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.1668632697255035</v>
+        <v>-0.1337417105586738</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.1060894614795913</v>
+        <v>-0.07493264121534082</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 1.768</t>
+          <t>X &lt; 1.765</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3938</v>
+        <v>3949</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.21566672656067</v>
+        <v>-0.213292036901116</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.24400085777539</v>
+        <v>-0.2432510408178956</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.3719076942230615</v>
+        <v>-0.370865282195922</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.3039634610161173</v>
+        <v>-0.303088803088805</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.3725158251318987</v>
+        <v>-0.3744364649972525</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.2640616074347975</v>
+        <v>-0.2647866662862128</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.2336050459707195</v>
+        <v>-0.235880364254605</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.1544138851931791</v>
+        <v>-0.1569853415268838</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.252171357717458</v>
+        <v>-0.2559349081782543</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.3017456198793553</v>
+        <v>-0.3069627976120444</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.4161756545099564</v>
+        <v>-0.4211098408664498</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.03767344902064451</v>
+        <v>-0.04511371167025402</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.0881383684927215</v>
+        <v>-0.0969648644322163</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.0004010475361582166</v>
+        <v>-0.01089668935249222</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 1.828</t>
+          <t>X &lt; 1.825</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3964</v>
+        <v>3972</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.1298976749899765</v>
+        <v>-0.1387191021768217</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.2440135924110578</v>
+        <v>-0.2529274642596988</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.348508728479004</v>
+        <v>-0.3318674707903853</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.3053146959173461</v>
+        <v>-0.288835473918347</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.326601648039258</v>
+        <v>-0.33747464064691</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.2168992356574861</v>
+        <v>-0.2268728109341467</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.1871848493551482</v>
+        <v>-0.1984746820976966</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.1115595159635063</v>
+        <v>-0.1227197632737926</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.1586747580556249</v>
+        <v>-0.1710131228341254</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.1630664247761686</v>
+        <v>-0.1761882693394483</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.252845178846961</v>
+        <v>-0.2656658971901322</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>0.04779926191570638</v>
+        <v>0.03303918216498403</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.005068270814604148</v>
+        <v>-0.02077972869000888</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>0.08359514163002046</v>
+        <v>0.06625134894139251</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 1.888</t>
+          <t>X &lt; 1.884</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3994</v>
+        <v>4004</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.02271787730250452</v>
+        <v>-0.033138959564603</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.2728310302382226</v>
+        <v>-0.2835279538675337</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.2796325595392375</v>
+        <v>-0.2902647563899166</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.2607442688607691</v>
+        <v>-0.2714428073172499</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.3358572283776695</v>
+        <v>-0.3485101142173832</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.199762788775196</v>
+        <v>-0.2116922220475388</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.1709020905308734</v>
+        <v>-0.1840007883966024</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.07434289127837701</v>
+        <v>-0.08762650095448521</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.1215528547528848</v>
+        <v>-0.1358207442075354</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.1322798621400167</v>
+        <v>-0.1475232653434233</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.2229134787484668</v>
+        <v>-0.237909439544481</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.000664381195349506</v>
+        <v>-0.01600652456429685</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.05497302249821701</v>
+        <v>-0.07256498453524785</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.03470748117869249</v>
+        <v>0.01574797517517368</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 1.948</t>
+          <t>X &lt; 1.944</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4018</v>
+        <v>4028</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.03735363906821476</v>
+        <v>-0.02310365859151631</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.2707621732259753</v>
+        <v>-0.2566552466764946</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.2798742529548619</v>
+        <v>-0.2656849820416198</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.2603226448045746</v>
+        <v>-0.2461968442651994</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.2885311634528094</v>
+        <v>-0.2761665831827145</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.2011406393432011</v>
+        <v>-0.1880762513273879</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.1729574773053031</v>
+        <v>-0.1609044520205174</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.07976038630818749</v>
+        <v>-0.06786925055050119</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.07733971347353474</v>
+        <v>-0.06640094074895586</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.1676530932607889</v>
+        <v>-0.1573250902650045</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.1843680314884395</v>
+        <v>-0.1739677527778767</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0.01321424449148623</v>
+        <v>0.02216202905687936</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.04459677774590176</v>
+        <v>-0.03640393119817276</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>0.02101097823613429</v>
+        <v>0.0280494770496631</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 2.007</t>
+          <t>X &lt; 2.004</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4033</v>
+        <v>4042</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.009339164493816554</v>
+        <v>0.01763170162350036</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.2231280815709837</v>
+        <v>-0.1959036115721915</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.2831148535559933</v>
+        <v>-0.2555933923126403</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.2384193269216652</v>
+        <v>-0.2357213369059394</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.2190348995527813</v>
+        <v>-0.2425904676084869</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.1803404286857457</v>
+        <v>-0.2032361089054859</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.1030663266995475</v>
+        <v>-0.126976818933521</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.03669124483123198</v>
+        <v>-0.06056963718504704</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.05926016419540048</v>
+        <v>-0.08394216584452607</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.1523914785129676</v>
+        <v>-0.1774066523015847</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.1945783026885195</v>
+        <v>-0.2194250998706693</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.05196103100501404</v>
+        <v>0.02567180857892026</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.03197699933341625</v>
+        <v>-0.05879293420118614</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.05902488959979024</v>
+        <v>0.03103451940778967</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 2.067</t>
+          <t>X &lt; 2.064</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4042</v>
+        <v>4053</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.02715524138515946</v>
+        <v>-0.02609805213735683</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.2687178118073561</v>
+        <v>-0.2679506566602967</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.3294592473120161</v>
+        <v>-0.3285623314284081</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.2352268445279364</v>
+        <v>-0.2345733272388557</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.2170805986801057</v>
+        <v>-0.218130058163716</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.1778108018057125</v>
+        <v>-0.1781373829941515</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.125593585599816</v>
+        <v>-0.1268734059397332</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.06041008495426325</v>
+        <v>-0.06190858338084126</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.05836062971367539</v>
+        <v>-0.06067562653796443</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.1531751342941376</v>
+        <v>-0.1561146603202843</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.1710018627125862</v>
+        <v>-0.1739127060174965</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.07507113215996952</v>
+        <v>0.07068834065944429</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.03434372363125959</v>
+        <v>-0.03927531886697011</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>0.08169780833196683</v>
+        <v>0.07566215426033551</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 2.127</t>
+          <t>X &lt; 2.123</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4057</v>
+        <v>4068</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.0239135735318996</v>
+        <v>-0.02297631888355056</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.2213722145296089</v>
+        <v>-0.2207398904349986</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.2833336853443669</v>
+        <v>-0.2825650204462917</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.2381334889350128</v>
+        <v>-0.2374763539550244</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.1482581342894775</v>
+        <v>-0.1493108109473695</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.1080189927765147</v>
+        <v>-0.1084445558214924</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.05628999552313019</v>
+        <v>-0.0575754519368985</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>0.03155792092935883</v>
+        <v>0.02999794553851842</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.01583957266574743</v>
+        <v>-0.01799109048891978</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.08880823713766262</v>
+        <v>-0.09154484889537429</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.1319400762828238</v>
+        <v>-0.134577619774646</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.1133602255985124</v>
+        <v>0.1093459872085845</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.02744888117510413</v>
+        <v>0.02291654828697887</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>0.119262462529214</v>
+        <v>0.1137817015274791</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 2.187</t>
+          <t>X &lt; 2.183</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4066</v>
+        <v>4077</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.007438958433539256</v>
+        <v>0.008225583425968352</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.1931320402239862</v>
+        <v>-0.1925796901846795</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.2067655858611914</v>
+        <v>-0.2062049805493231</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.210426578700087</v>
+        <v>-0.209846551784409</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.1219317828912239</v>
+        <v>-0.1229460852215567</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.05657223383175136</v>
+        <v>-0.05708261146679661</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.05423594648500085</v>
+        <v>-0.05541829817810395</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.05694394565679772</v>
+        <v>0.05542757094389827</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.009522655465865171</v>
+        <v>0.007469053649295176</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.04058782447498999</v>
+        <v>-0.04322928041447938</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.08406517933885738</v>
+        <v>-0.08660559382350641</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.1361981450476932</v>
+        <v>0.1324041029364693</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>0.07414091479677154</v>
+        <v>0.06982078999009644</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>0.1662624131832047</v>
+        <v>0.1610466304076041</v>
       </c>
     </row>
   </sheetData>
